--- a/02-Referencias/Custos-Maquinas/medias_consumo_diesel_tratado.xlsx
+++ b/02-Referencias/Custos-Maquinas/medias_consumo_diesel_tratado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julio.santana\Documents\Projects\Cofre_Trabalho\02-Referencias\Custos-Maquinas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEA0D66-DD86-4C46-9F29-CCC076EA7747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370C8B5E-D8A6-47C6-B75D-3ED4D62F8374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,11 +228,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="167" formatCode="0.00\L"/>
     <numFmt numFmtId="169" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -376,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -422,6 +424,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -735,8 +749,8 @@
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" style="5" customWidth="1"/>
     <col min="10" max="10" width="21" style="5" customWidth="1"/>
     <col min="11" max="11" width="24" style="5" customWidth="1"/>
@@ -785,33 +799,35 @@
       <c r="N3" s="4"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="5">
         <v>17</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>17</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>348</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>57</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <v>88470</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="27">
         <v>577089.10000000009</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="28">
         <v>14.086502160858331</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -878,13 +894,13 @@
       <c r="E8" s="18">
         <v>4</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="25">
         <v>1089.5</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="25">
         <v>6464.7400000000007</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="25">
         <v>721.3</v>
       </c>
       <c r="I8" s="11">
@@ -918,13 +934,13 @@
       <c r="E9" s="18">
         <v>3</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="25">
         <v>819</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="25">
         <v>5520.6900000000014</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="25">
         <v>86.3</v>
       </c>
       <c r="I9" s="11">
@@ -958,13 +974,13 @@
       <c r="E10" s="18">
         <v>7</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="25">
         <v>3606.5</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="25">
         <v>42618.250000000007</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="25">
         <v>382</v>
       </c>
       <c r="I10" s="11">
@@ -998,13 +1014,13 @@
       <c r="E11" s="18">
         <v>11</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="25">
         <v>2838</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="25">
         <v>18106.490000000002</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="25">
         <v>198</v>
       </c>
       <c r="I11" s="11">
@@ -1038,13 +1054,13 @@
       <c r="E12" s="18">
         <v>11</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="25">
         <v>2466.5</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="25">
         <v>14411.32</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="25">
         <v>158</v>
       </c>
       <c r="I12" s="11">
@@ -1078,13 +1094,13 @@
       <c r="E13" s="18">
         <v>9</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="25">
         <v>2175.5</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="25">
         <v>13065.43</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="25">
         <v>194</v>
       </c>
       <c r="I13" s="11">
@@ -1118,13 +1134,13 @@
       <c r="E14" s="18">
         <v>7</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="25">
         <v>1863</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="25">
         <v>10378.06</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="25">
         <v>98.5</v>
       </c>
       <c r="I14" s="11">
@@ -1158,13 +1174,13 @@
       <c r="E15" s="18">
         <v>16</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="25">
         <v>4548</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="25">
         <v>28873.79</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="25">
         <v>275</v>
       </c>
       <c r="I15" s="11">
@@ -1198,13 +1214,13 @@
       <c r="E16" s="18">
         <v>29</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="25">
         <v>10541.5</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="25">
         <v>66694.820000000007</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="25">
         <v>780.8</v>
       </c>
       <c r="I16" s="11">
@@ -1238,13 +1254,13 @@
       <c r="E17" s="18">
         <v>38</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="25">
         <v>11615.5</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="25">
         <v>72359.19</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="25">
         <v>775</v>
       </c>
       <c r="I17" s="11">
@@ -1278,13 +1294,13 @@
       <c r="E18" s="18">
         <v>27</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="25">
         <v>8638</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="25">
         <v>51832.35</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="25">
         <v>1083.3</v>
       </c>
       <c r="I18" s="11">
@@ -1318,13 +1334,13 @@
       <c r="E19" s="18">
         <v>26</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="25">
         <v>8032.5</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="25">
         <v>48721.81</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="25">
         <v>693</v>
       </c>
       <c r="I19" s="11">
@@ -1358,13 +1374,13 @@
       <c r="E20" s="18">
         <v>40</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="25">
         <v>11212.5</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="25">
         <v>84584.659999999989</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="25">
         <v>1067</v>
       </c>
       <c r="I20" s="11">
@@ -1398,13 +1414,13 @@
       <c r="E21" s="18">
         <v>27</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="25">
         <v>7984.5</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="25">
         <v>45681.31</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="25">
         <v>895</v>
       </c>
       <c r="I21" s="11">
@@ -1438,13 +1454,13 @@
       <c r="E22" s="18">
         <v>18</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="25">
         <v>5555</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="25">
         <v>34571.39</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="25">
         <v>494</v>
       </c>
       <c r="I22" s="11">
@@ -1478,13 +1494,13 @@
       <c r="E23" s="18">
         <v>8</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="25">
         <v>2448.5</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="25">
         <v>14867.36</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="25">
         <v>359</v>
       </c>
       <c r="I23" s="11">
@@ -1518,13 +1534,13 @@
       <c r="E24" s="22">
         <v>10</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="26">
         <v>3036</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="26">
         <v>18337.439999999999</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="26">
         <v>174</v>
       </c>
       <c r="I24" s="15">
@@ -1610,13 +1626,13 @@
       <c r="F28" s="10">
         <v>9999.6</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="18">
         <v>0.3</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="25">
         <v>315</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="25">
         <v>0</v>
       </c>
       <c r="J28" s="18" t="b">
@@ -1652,13 +1668,13 @@
       <c r="F29" s="10">
         <v>9999.7000000000007</v>
       </c>
-      <c r="G29" s="10">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10">
+      <c r="G29" s="18">
+        <v>0</v>
+      </c>
+      <c r="H29" s="25">
         <v>2034.9999999925969</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="25">
         <v>0</v>
       </c>
       <c r="J29" s="18" t="b">
@@ -1692,13 +1708,13 @@
       <c r="F30" s="10">
         <v>9999.7999999999993</v>
       </c>
-      <c r="G30" s="10">
-        <v>0</v>
-      </c>
-      <c r="H30" s="10">
+      <c r="G30" s="18">
+        <v>0</v>
+      </c>
+      <c r="H30" s="25">
         <v>2240.0000000325958</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="25">
         <v>0</v>
       </c>
       <c r="J30" s="18" t="b">
@@ -1732,13 +1748,13 @@
       <c r="F31" s="10">
         <v>9999.9</v>
       </c>
-      <c r="G31" s="10">
-        <v>0</v>
-      </c>
-      <c r="H31" s="10">
+      <c r="G31" s="18">
+        <v>0</v>
+      </c>
+      <c r="H31" s="25">
         <v>24.999999999909051</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="25">
         <v>24.999999999909051</v>
       </c>
       <c r="J31" s="18" t="b">
@@ -1770,13 +1786,13 @@
       <c r="F32" s="10">
         <v>10000</v>
       </c>
-      <c r="G32" s="10">
-        <v>0</v>
-      </c>
-      <c r="H32" s="10">
+      <c r="G32" s="18">
+        <v>0</v>
+      </c>
+      <c r="H32" s="25">
         <v>1584.999999994234</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="25">
         <v>0</v>
       </c>
       <c r="J32" s="18" t="b">
@@ -1810,13 +1826,13 @@
       <c r="F33" s="10">
         <v>10446.799999999999</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="18">
         <v>447</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="25">
         <v>0.139883616830797</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="25">
         <v>0</v>
       </c>
       <c r="J33" s="18" t="b">
@@ -1852,13 +1868,13 @@
       <c r="F34" s="10">
         <v>10455.799999999999</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="18">
         <v>9</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="25">
         <v>7.2222222222222223</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="25">
         <v>7.2222222222222223</v>
       </c>
       <c r="J34" s="18" t="b">
@@ -1892,13 +1908,13 @@
       <c r="F35" s="10">
         <v>10459.200000000001</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="18">
         <v>3</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="25">
         <v>19.70588235293274</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="25">
         <v>19.70588235293274</v>
       </c>
       <c r="J35" s="18" t="b">
@@ -1932,13 +1948,13 @@
       <c r="F36" s="10">
         <v>10463.9</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="18">
         <v>5</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="25">
         <v>13.93617021276919</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="25">
         <v>13.93617021276919</v>
       </c>
       <c r="J36" s="18" t="b">
@@ -1972,13 +1988,13 @@
       <c r="F37" s="10">
         <v>10633.9</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="18">
         <v>170</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="25">
         <v>0.23529411764705879</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="25">
         <v>0</v>
       </c>
       <c r="J37" s="18" t="b">
@@ -2014,13 +2030,13 @@
       <c r="F38" s="10">
         <v>10721</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="18">
         <v>87</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="25">
         <v>1.222732491389203</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="25">
         <v>0</v>
       </c>
       <c r="J38" s="18" t="b">
@@ -2056,13 +2072,13 @@
       <c r="F39" s="10">
         <v>13491.5</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="18">
         <v>16.3</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="25">
         <v>10.846</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="25">
         <v>10.846</v>
       </c>
       <c r="J39" s="18" t="b">
@@ -2096,13 +2112,13 @@
       <c r="F40" s="10">
         <v>13543.6</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="18">
         <v>52</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="25">
         <v>6.0268714011515891</v>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="25">
         <v>6.0268714011515891</v>
       </c>
       <c r="J40" s="18" t="b">
@@ -2136,13 +2152,13 @@
       <c r="F41" s="10">
         <v>13562</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="18">
         <v>18</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="25">
         <v>17.907608695652531</v>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="25">
         <v>17.907608695652531</v>
       </c>
       <c r="J41" s="18" t="b">
@@ -2176,13 +2192,13 @@
       <c r="F42" s="10">
         <v>9137.7000000000007</v>
       </c>
-      <c r="G42" s="10">
-        <v>0</v>
-      </c>
-      <c r="H42" s="10">
-        <v>0</v>
-      </c>
-      <c r="I42" s="18">
+      <c r="G42" s="18">
+        <v>0</v>
+      </c>
+      <c r="H42" s="25">
+        <v>0</v>
+      </c>
+      <c r="I42" s="25">
         <v>0</v>
       </c>
       <c r="J42" s="18" t="b">
@@ -2218,11 +2234,11 @@
       <c r="F43" s="10">
         <v>9137.7000000000007</v>
       </c>
-      <c r="G43" s="10">
-        <v>0</v>
-      </c>
-      <c r="H43" s="10"/>
-      <c r="I43" s="18">
+      <c r="G43" s="18">
+        <v>0</v>
+      </c>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25">
         <v>0</v>
       </c>
       <c r="J43" s="18" t="b">
@@ -2258,13 +2274,13 @@
       <c r="F44" s="10">
         <v>9178</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="18">
         <v>40</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="25">
         <v>5.2481389578164723</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="25">
         <v>5.2481389578164723</v>
       </c>
       <c r="J44" s="18" t="b">
@@ -2300,13 +2316,13 @@
       <c r="F45" s="10">
         <v>9203.6</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="18">
         <v>26</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="25">
         <v>11.23046874999984</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="25">
         <v>11.23046874999984</v>
       </c>
       <c r="J45" s="18" t="b">
@@ -2342,13 +2358,13 @@
       <c r="F46" s="10">
         <v>9207.6</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="18">
         <v>4</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="25">
         <v>56</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="25">
         <v>0</v>
       </c>
       <c r="J46" s="18" t="b">
@@ -2386,13 +2402,13 @@
       <c r="F47" s="10">
         <v>9238.9</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="18">
         <v>31</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="25">
         <v>11.59744408945714</v>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="25">
         <v>11.59744408945714</v>
       </c>
       <c r="J47" s="18" t="b">
@@ -2428,13 +2444,13 @@
       <c r="F48" s="10">
         <v>9269.9</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="18">
         <v>31</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="25">
         <v>14.32258064516129</v>
       </c>
-      <c r="I48" s="18">
+      <c r="I48" s="25">
         <v>14.32258064516129</v>
       </c>
       <c r="J48" s="18" t="b">
@@ -2470,11 +2486,11 @@
       <c r="F49" s="10">
         <v>9269.9</v>
       </c>
-      <c r="G49" s="10">
-        <v>0</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="18">
+      <c r="G49" s="18">
+        <v>0</v>
+      </c>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25">
         <v>0</v>
       </c>
       <c r="J49" s="18" t="b">
@@ -2510,13 +2526,13 @@
       <c r="F50" s="10">
         <v>9314.2000000000007</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="18">
         <v>44</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="25">
         <v>10.225733634311259</v>
       </c>
-      <c r="I50" s="18">
+      <c r="I50" s="25">
         <v>10.225733634311259</v>
       </c>
       <c r="J50" s="18" t="b">
@@ -2552,13 +2568,13 @@
       <c r="F51" s="10">
         <v>9355.2000000000007</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="18">
         <v>41</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="25">
         <v>10.34146341463415</v>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="25">
         <v>10.34146341463415</v>
       </c>
       <c r="J51" s="18" t="b">
@@ -2594,13 +2610,13 @@
       <c r="F52" s="10">
         <v>9409.2999999999993</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="18">
         <v>54</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="25">
         <v>2.1072088724584672</v>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="25">
         <v>0</v>
       </c>
       <c r="J52" s="18" t="b">
@@ -2638,13 +2654,13 @@
       <c r="F53" s="10">
         <v>9420.7000000000007</v>
       </c>
-      <c r="G53" s="10">
-        <v>11</v>
-      </c>
-      <c r="H53" s="10">
+      <c r="G53" s="18">
+        <v>11</v>
+      </c>
+      <c r="H53" s="25">
         <v>21.140350877190279</v>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="25">
         <v>21.140350877190279</v>
       </c>
       <c r="J53" s="18" t="b">
@@ -2680,13 +2696,13 @@
       <c r="F54" s="10">
         <v>9520</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="18">
         <v>99</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="25">
         <v>2.5176233635448322E-2</v>
       </c>
-      <c r="I54" s="18">
+      <c r="I54" s="25">
         <v>0</v>
       </c>
       <c r="J54" s="18" t="b">
@@ -2724,13 +2740,13 @@
       <c r="F55" s="10">
         <v>9520.7000000000007</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="18">
         <v>1</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="25">
         <v>0.7142857142849719</v>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="25">
         <v>0</v>
       </c>
       <c r="J55" s="18" t="b">
@@ -2768,11 +2784,11 @@
       <c r="F56" s="10">
         <v>9520.7000000000007</v>
       </c>
-      <c r="G56" s="10">
-        <v>0</v>
-      </c>
-      <c r="H56" s="10"/>
-      <c r="I56" s="18">
+      <c r="G56" s="18">
+        <v>0</v>
+      </c>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25">
         <v>0</v>
       </c>
       <c r="J56" s="18" t="b">
@@ -2808,13 +2824,13 @@
       <c r="F57" s="10">
         <v>9417.6</v>
       </c>
-      <c r="G57" s="10">
-        <v>0</v>
-      </c>
-      <c r="H57" s="10">
+      <c r="G57" s="18">
+        <v>0</v>
+      </c>
+      <c r="H57" s="25">
         <v>1.810440027183146E-2</v>
       </c>
-      <c r="I57" s="18">
+      <c r="I57" s="25">
         <v>0</v>
       </c>
       <c r="J57" s="18" t="b">
@@ -2848,13 +2864,13 @@
       <c r="F58" s="10">
         <v>9433.7999999999993</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="18">
         <v>16</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="25">
         <v>12.93209876543297</v>
       </c>
-      <c r="I58" s="18">
+      <c r="I58" s="25">
         <v>12.93209876543297</v>
       </c>
       <c r="J58" s="18" t="b">
@@ -2888,13 +2904,13 @@
       <c r="F59" s="10">
         <v>9448.1</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59" s="18">
         <v>14</v>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="25">
         <v>16.36363636363512</v>
       </c>
-      <c r="I59" s="18">
+      <c r="I59" s="25">
         <v>16.36363636363512</v>
       </c>
       <c r="J59" s="18" t="b">
@@ -2928,13 +2944,13 @@
       <c r="F60" s="10">
         <v>9466</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G60" s="18">
         <v>18</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="25">
         <v>15.083798882681871</v>
       </c>
-      <c r="I60" s="18">
+      <c r="I60" s="25">
         <v>15.083798882681871</v>
       </c>
       <c r="J60" s="18" t="b">
@@ -2968,13 +2984,13 @@
       <c r="F61" s="10">
         <v>9481.2999999999993</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G61" s="18">
         <v>15</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H61" s="25">
         <v>15.228758169935359</v>
       </c>
-      <c r="I61" s="18">
+      <c r="I61" s="25">
         <v>15.228758169935359</v>
       </c>
       <c r="J61" s="18" t="b">
@@ -3008,13 +3024,13 @@
       <c r="F62" s="10">
         <v>9493.2000000000007</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G62" s="18">
         <v>12</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="25">
         <v>16.680672268905521</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="25">
         <v>16.680672268905521</v>
       </c>
       <c r="J62" s="18" t="b">
@@ -3048,13 +3064,13 @@
       <c r="F63" s="10">
         <v>9506</v>
       </c>
-      <c r="G63" s="10">
+      <c r="G63" s="18">
         <v>13</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="25">
         <v>19.96093750000113</v>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="25">
         <v>19.96093750000113</v>
       </c>
       <c r="J63" s="18" t="b">
@@ -3088,13 +3104,13 @@
       <c r="F64" s="10">
         <v>9520.7000000000007</v>
       </c>
-      <c r="G64" s="10">
+      <c r="G64" s="18">
         <v>15</v>
       </c>
-      <c r="H64" s="10">
+      <c r="H64" s="25">
         <v>17.925170068026318</v>
       </c>
-      <c r="I64" s="18">
+      <c r="I64" s="25">
         <v>17.925170068026318</v>
       </c>
       <c r="J64" s="18" t="b">
@@ -3128,13 +3144,13 @@
       <c r="F65" s="10">
         <v>9538</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G65" s="18">
         <v>17</v>
       </c>
-      <c r="H65" s="10">
+      <c r="H65" s="25">
         <v>16.242774566474669</v>
       </c>
-      <c r="I65" s="18">
+      <c r="I65" s="25">
         <v>16.242774566474669</v>
       </c>
       <c r="J65" s="18" t="b">
@@ -3166,13 +3182,13 @@
       <c r="F66" s="10">
         <v>9552.2000000000007</v>
       </c>
-      <c r="G66" s="10">
+      <c r="G66" s="18">
         <v>14</v>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="25">
         <v>3.5211267605632E-2</v>
       </c>
-      <c r="I66" s="18">
+      <c r="I66" s="25">
         <v>0</v>
       </c>
       <c r="J66" s="18" t="b">
@@ -3208,11 +3224,11 @@
       <c r="F67" s="10">
         <v>9552.2000000000007</v>
       </c>
-      <c r="G67" s="10">
-        <v>0</v>
-      </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="18">
+      <c r="G67" s="18">
+        <v>0</v>
+      </c>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25">
         <v>0</v>
       </c>
       <c r="J67" s="18" t="b">
@@ -3246,13 +3262,13 @@
       <c r="F68" s="10">
         <v>9588.1</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G68" s="18">
         <v>36</v>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="25">
         <v>6.2534818941504824</v>
       </c>
-      <c r="I68" s="18">
+      <c r="I68" s="25">
         <v>6.2534818941504824</v>
       </c>
       <c r="J68" s="18" t="b">
@@ -3286,13 +3302,13 @@
       <c r="F69" s="10">
         <v>9602.1</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69" s="18">
         <v>14</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="25">
         <v>16.607142857142861</v>
       </c>
-      <c r="I69" s="18">
+      <c r="I69" s="25">
         <v>16.607142857142861</v>
       </c>
       <c r="J69" s="18" t="b">
@@ -3326,13 +3342,13 @@
       <c r="F70" s="10">
         <v>9616</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70" s="18">
         <v>14</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="25">
         <v>18.92086330935301</v>
       </c>
-      <c r="I70" s="18">
+      <c r="I70" s="25">
         <v>18.92086330935301</v>
       </c>
       <c r="J70" s="18" t="b">
@@ -3366,13 +3382,13 @@
       <c r="F71" s="10">
         <v>10.4</v>
       </c>
-      <c r="G71" s="10">
+      <c r="G71" s="18">
         <v>10</v>
       </c>
-      <c r="H71" s="10">
+      <c r="H71" s="25">
         <v>22.06730769230769</v>
       </c>
-      <c r="I71" s="18">
+      <c r="I71" s="25">
         <v>22.06730769230769</v>
       </c>
       <c r="J71" s="18" t="b">
@@ -3408,13 +3424,13 @@
       <c r="F72" s="10">
         <v>19.2</v>
       </c>
-      <c r="G72" s="10">
+      <c r="G72" s="18">
         <v>9</v>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="25">
         <v>13.86363636363637</v>
       </c>
-      <c r="I72" s="18">
+      <c r="I72" s="25">
         <v>13.86363636363637</v>
       </c>
       <c r="J72" s="18" t="b">
@@ -3450,13 +3466,13 @@
       <c r="F73" s="10">
         <v>30</v>
       </c>
-      <c r="G73" s="10">
-        <v>11</v>
-      </c>
-      <c r="H73" s="10">
+      <c r="G73" s="18">
+        <v>11</v>
+      </c>
+      <c r="H73" s="25">
         <v>7.4074074074074074</v>
       </c>
-      <c r="I73" s="18">
+      <c r="I73" s="25">
         <v>7.4074074074074074</v>
       </c>
       <c r="J73" s="18" t="b">
@@ -3492,13 +3508,13 @@
       <c r="F74" s="10">
         <v>31.2</v>
       </c>
-      <c r="G74" s="10">
+      <c r="G74" s="18">
         <v>1</v>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="25">
         <v>164.5833333333334</v>
       </c>
-      <c r="I74" s="18">
+      <c r="I74" s="25">
         <v>0</v>
       </c>
       <c r="J74" s="18" t="b">
@@ -3536,13 +3552,13 @@
       <c r="F75" s="10">
         <v>37.5</v>
       </c>
-      <c r="G75" s="10">
+      <c r="G75" s="18">
         <v>6</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="25">
         <v>24.603174603174601</v>
       </c>
-      <c r="I75" s="18">
+      <c r="I75" s="25">
         <v>24.603174603174601</v>
       </c>
       <c r="J75" s="18" t="b">
@@ -3578,13 +3594,13 @@
       <c r="F76" s="10">
         <v>37.6</v>
       </c>
-      <c r="G76" s="10">
-        <v>0</v>
-      </c>
-      <c r="H76" s="10">
+      <c r="G76" s="18">
+        <v>0</v>
+      </c>
+      <c r="H76" s="25">
         <v>1604.999999999977</v>
       </c>
-      <c r="I76" s="18">
+      <c r="I76" s="25">
         <v>0</v>
       </c>
       <c r="J76" s="18" t="b">
@@ -3620,13 +3636,13 @@
       <c r="F77" s="10">
         <v>41.1</v>
       </c>
-      <c r="G77" s="10">
+      <c r="G77" s="18">
         <v>4</v>
       </c>
-      <c r="H77" s="10">
+      <c r="H77" s="25">
         <v>79</v>
       </c>
-      <c r="I77" s="18">
+      <c r="I77" s="25">
         <v>0</v>
       </c>
       <c r="J77" s="18" t="b">
@@ -3664,13 +3680,13 @@
       <c r="F78" s="10">
         <v>51.8</v>
       </c>
-      <c r="G78" s="10">
-        <v>11</v>
-      </c>
-      <c r="H78" s="10">
+      <c r="G78" s="18">
+        <v>11</v>
+      </c>
+      <c r="H78" s="25">
         <v>3.691588785046731</v>
       </c>
-      <c r="I78" s="18">
+      <c r="I78" s="25">
         <v>3.691588785046731</v>
       </c>
       <c r="J78" s="18" t="b">
@@ -3706,11 +3722,11 @@
       <c r="F79" s="10">
         <v>51.8</v>
       </c>
-      <c r="G79" s="10">
-        <v>0</v>
-      </c>
-      <c r="H79" s="10"/>
-      <c r="I79" s="18">
+      <c r="G79" s="18">
+        <v>0</v>
+      </c>
+      <c r="H79" s="25"/>
+      <c r="I79" s="25">
         <v>0</v>
       </c>
       <c r="J79" s="18" t="b">
@@ -3744,11 +3760,11 @@
       <c r="F80" s="10">
         <v>51.8</v>
       </c>
-      <c r="G80" s="10">
-        <v>0</v>
-      </c>
-      <c r="H80" s="10"/>
-      <c r="I80" s="18">
+      <c r="G80" s="18">
+        <v>0</v>
+      </c>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25">
         <v>0</v>
       </c>
       <c r="J80" s="18" t="b">
@@ -3780,13 +3796,13 @@
       <c r="F81" s="10">
         <v>5.5</v>
       </c>
-      <c r="G81" s="10">
+      <c r="G81" s="18">
         <v>6</v>
       </c>
-      <c r="H81" s="10">
+      <c r="H81" s="25">
         <v>34.363636363636367</v>
       </c>
-      <c r="I81" s="18">
+      <c r="I81" s="25">
         <v>34.363636363636367</v>
       </c>
       <c r="J81" s="18" t="b">
@@ -3820,13 +3836,13 @@
       <c r="F82" s="10">
         <v>22.3</v>
       </c>
-      <c r="G82" s="10">
+      <c r="G82" s="18">
         <v>17</v>
       </c>
-      <c r="H82" s="10">
+      <c r="H82" s="25">
         <v>8.3928571428571423</v>
       </c>
-      <c r="I82" s="18">
+      <c r="I82" s="25">
         <v>8.3928571428571423</v>
       </c>
       <c r="J82" s="18" t="b">
@@ -3860,13 +3876,13 @@
       <c r="F83" s="10">
         <v>33.9</v>
       </c>
-      <c r="G83" s="10">
+      <c r="G83" s="18">
         <v>12</v>
       </c>
-      <c r="H83" s="10">
+      <c r="H83" s="25">
         <v>12.801724137931039</v>
       </c>
-      <c r="I83" s="18">
+      <c r="I83" s="25">
         <v>12.801724137931039</v>
       </c>
       <c r="J83" s="18" t="b">
@@ -3900,13 +3916,13 @@
       <c r="F84" s="10">
         <v>66.099999999999994</v>
       </c>
-      <c r="G84" s="10">
+      <c r="G84" s="18">
         <v>32</v>
       </c>
-      <c r="H84" s="10">
+      <c r="H84" s="25">
         <v>7.1273291925465836</v>
       </c>
-      <c r="I84" s="18">
+      <c r="I84" s="25">
         <v>7.1273291925465836</v>
       </c>
       <c r="J84" s="18" t="b">
@@ -3940,13 +3956,13 @@
       <c r="F85" s="10">
         <v>88.9</v>
       </c>
-      <c r="G85" s="10">
+      <c r="G85" s="18">
         <v>23</v>
       </c>
-      <c r="H85" s="10">
+      <c r="H85" s="25">
         <v>7.4561403508771891</v>
       </c>
-      <c r="I85" s="18">
+      <c r="I85" s="25">
         <v>7.4561403508771891</v>
       </c>
       <c r="J85" s="18" t="b">
@@ -3980,13 +3996,13 @@
       <c r="F86" s="10">
         <v>105</v>
       </c>
-      <c r="G86" s="10">
+      <c r="G86" s="18">
         <v>16</v>
       </c>
-      <c r="H86" s="10">
+      <c r="H86" s="25">
         <v>8.6956521739130466</v>
       </c>
-      <c r="I86" s="18">
+      <c r="I86" s="25">
         <v>8.6956521739130466</v>
       </c>
       <c r="J86" s="18" t="b">
@@ -4020,13 +4036,13 @@
       <c r="F87" s="10">
         <v>4421.2</v>
       </c>
-      <c r="G87" s="10">
+      <c r="G87" s="18">
         <v>21</v>
       </c>
-      <c r="H87" s="10">
+      <c r="H87" s="25">
         <v>10.928571428571431</v>
       </c>
-      <c r="I87" s="18">
+      <c r="I87" s="25">
         <v>10.928571428571431</v>
       </c>
       <c r="J87" s="18" t="b">
@@ -4062,13 +4078,13 @@
       <c r="F88" s="10">
         <v>4443.5</v>
       </c>
-      <c r="G88" s="10">
+      <c r="G88" s="18">
         <v>22</v>
       </c>
-      <c r="H88" s="10">
+      <c r="H88" s="25">
         <v>11.278026905829501</v>
       </c>
-      <c r="I88" s="18">
+      <c r="I88" s="25">
         <v>11.278026905829501</v>
       </c>
       <c r="J88" s="18" t="b">
@@ -4104,13 +4120,13 @@
       <c r="F89" s="10">
         <v>4467.1000000000004</v>
       </c>
-      <c r="G89" s="10">
+      <c r="G89" s="18">
         <v>24</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="25">
         <v>10.42372881355916</v>
       </c>
-      <c r="I89" s="18">
+      <c r="I89" s="25">
         <v>10.42372881355916</v>
       </c>
       <c r="J89" s="18" t="b">
@@ -4146,13 +4162,13 @@
       <c r="F90" s="10">
         <v>4489.2</v>
       </c>
-      <c r="G90" s="10">
+      <c r="G90" s="18">
         <v>22</v>
       </c>
-      <c r="H90" s="10">
+      <c r="H90" s="25">
         <v>9.5475113122174307</v>
       </c>
-      <c r="I90" s="18">
+      <c r="I90" s="25">
         <v>9.5475113122174307</v>
       </c>
       <c r="J90" s="18" t="b">
@@ -4188,13 +4204,13 @@
       <c r="F91" s="10">
         <v>4507.8</v>
       </c>
-      <c r="G91" s="10">
+      <c r="G91" s="18">
         <v>19</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="25">
         <v>14.139784946236279</v>
       </c>
-      <c r="I91" s="18">
+      <c r="I91" s="25">
         <v>14.139784946236279</v>
       </c>
       <c r="J91" s="18" t="b">
@@ -4230,13 +4246,13 @@
       <c r="F92" s="10">
         <v>4530.5</v>
       </c>
-      <c r="G92" s="10">
+      <c r="G92" s="18">
         <v>23</v>
       </c>
-      <c r="H92" s="10">
+      <c r="H92" s="25">
         <v>10.90308370044062</v>
       </c>
-      <c r="I92" s="18">
+      <c r="I92" s="25">
         <v>10.90308370044062</v>
       </c>
       <c r="J92" s="18" t="b">
@@ -4272,13 +4288,13 @@
       <c r="F93" s="10">
         <v>4552.3999999999996</v>
       </c>
-      <c r="G93" s="10">
+      <c r="G93" s="18">
         <v>22</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="25">
         <v>11.529680365297001</v>
       </c>
-      <c r="I93" s="18">
+      <c r="I93" s="25">
         <v>11.529680365297001</v>
       </c>
       <c r="J93" s="18" t="b">
@@ -4314,13 +4330,13 @@
       <c r="F94" s="10">
         <v>4574.3</v>
       </c>
-      <c r="G94" s="10">
+      <c r="G94" s="18">
         <v>22</v>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="25">
         <v>10.84474885844722</v>
       </c>
-      <c r="I94" s="18">
+      <c r="I94" s="25">
         <v>10.84474885844722</v>
       </c>
       <c r="J94" s="18" t="b">
@@ -4356,13 +4372,13 @@
       <c r="F95" s="10">
         <v>4593.6000000000004</v>
       </c>
-      <c r="G95" s="10">
+      <c r="G95" s="18">
         <v>19</v>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="25">
         <v>12.27979274611387</v>
       </c>
-      <c r="I95" s="18">
+      <c r="I95" s="25">
         <v>12.27979274611387</v>
       </c>
       <c r="J95" s="18" t="b">
@@ -4398,13 +4414,13 @@
       <c r="F96" s="10">
         <v>5521.3</v>
       </c>
-      <c r="G96" s="10">
+      <c r="G96" s="18">
         <v>13.5</v>
       </c>
-      <c r="H96" s="10">
+      <c r="H96" s="25">
         <v>17.481000000000002</v>
       </c>
-      <c r="I96" s="18">
+      <c r="I96" s="25">
         <v>17.481000000000002</v>
       </c>
       <c r="J96" s="18" t="b">
@@ -4440,13 +4456,13 @@
       <c r="F97" s="10">
         <v>5535.8</v>
       </c>
-      <c r="G97" s="10">
+      <c r="G97" s="18">
         <v>15</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="25">
         <v>18.03448275862069</v>
       </c>
-      <c r="I97" s="18">
+      <c r="I97" s="25">
         <v>18.03448275862069</v>
       </c>
       <c r="J97" s="18" t="b">
@@ -4482,13 +4498,13 @@
       <c r="F98" s="10">
         <v>5549.6</v>
       </c>
-      <c r="G98" s="10">
+      <c r="G98" s="18">
         <v>14</v>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="25">
         <v>19.202898550724381</v>
       </c>
-      <c r="I98" s="18">
+      <c r="I98" s="25">
         <v>19.202898550724381</v>
       </c>
       <c r="J98" s="18" t="b">
@@ -4524,13 +4540,13 @@
       <c r="F99" s="10">
         <v>5564.4</v>
       </c>
-      <c r="G99" s="10">
+      <c r="G99" s="18">
         <v>15</v>
       </c>
-      <c r="H99" s="10">
+      <c r="H99" s="25">
         <v>19.256756756757699</v>
       </c>
-      <c r="I99" s="18">
+      <c r="I99" s="25">
         <v>19.256756756757699</v>
       </c>
       <c r="J99" s="18" t="b">
@@ -4566,13 +4582,13 @@
       <c r="F100" s="10">
         <v>5579</v>
       </c>
-      <c r="G100" s="10">
+      <c r="G100" s="18">
         <v>15</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="25">
         <v>19.69178082191732</v>
       </c>
-      <c r="I100" s="18">
+      <c r="I100" s="25">
         <v>19.69178082191732</v>
       </c>
       <c r="J100" s="18" t="b">
@@ -4608,13 +4624,13 @@
       <c r="F101" s="10">
         <v>5591.4</v>
       </c>
-      <c r="G101" s="10">
+      <c r="G101" s="18">
         <v>12</v>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="25">
         <v>21.653225806452252</v>
       </c>
-      <c r="I101" s="18">
+      <c r="I101" s="25">
         <v>21.653225806452252</v>
       </c>
       <c r="J101" s="18" t="b">
@@ -4650,13 +4666,13 @@
       <c r="F102" s="10">
         <v>5605.6</v>
       </c>
-      <c r="G102" s="10">
+      <c r="G102" s="18">
         <v>14</v>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="25">
         <v>18.521126760562431</v>
       </c>
-      <c r="I102" s="18">
+      <c r="I102" s="25">
         <v>18.521126760562431</v>
       </c>
       <c r="J102" s="18" t="b">
@@ -4692,13 +4708,13 @@
       <c r="F103" s="10">
         <v>12972.8</v>
       </c>
-      <c r="G103" s="10">
-        <v>0</v>
-      </c>
-      <c r="H103" s="10">
+      <c r="G103" s="18">
+        <v>0</v>
+      </c>
+      <c r="H103" s="25">
         <v>2.189195855944746E-2</v>
       </c>
-      <c r="I103" s="18">
+      <c r="I103" s="25">
         <v>0</v>
       </c>
       <c r="J103" s="18" t="b">
@@ -4732,13 +4748,13 @@
       <c r="F104" s="10">
         <v>13000.5</v>
       </c>
-      <c r="G104" s="10">
+      <c r="G104" s="18">
         <v>28</v>
       </c>
-      <c r="H104" s="10">
+      <c r="H104" s="25">
         <v>12.3104693140791</v>
       </c>
-      <c r="I104" s="18">
+      <c r="I104" s="25">
         <v>12.3104693140791</v>
       </c>
       <c r="J104" s="18" t="b">
@@ -4772,13 +4788,13 @@
       <c r="F105" s="10">
         <v>13021.2</v>
       </c>
-      <c r="G105" s="10">
+      <c r="G105" s="18">
         <v>21</v>
       </c>
-      <c r="H105" s="10">
+      <c r="H105" s="25">
         <v>13.69565217391256</v>
       </c>
-      <c r="I105" s="18">
+      <c r="I105" s="25">
         <v>13.69565217391256</v>
       </c>
       <c r="J105" s="18" t="b">
@@ -4812,13 +4828,13 @@
       <c r="F106" s="10">
         <v>13037.2</v>
       </c>
-      <c r="G106" s="10">
+      <c r="G106" s="18">
         <v>16</v>
       </c>
-      <c r="H106" s="10">
+      <c r="H106" s="25">
         <v>17.90625</v>
       </c>
-      <c r="I106" s="18">
+      <c r="I106" s="25">
         <v>17.90625</v>
       </c>
       <c r="J106" s="18" t="b">
@@ -4852,13 +4868,13 @@
       <c r="F107" s="10">
         <v>13055</v>
       </c>
-      <c r="G107" s="10">
+      <c r="G107" s="18">
         <v>18</v>
       </c>
-      <c r="H107" s="10">
+      <c r="H107" s="25">
         <v>15.449438202247819</v>
       </c>
-      <c r="I107" s="18">
+      <c r="I107" s="25">
         <v>15.449438202247819</v>
       </c>
       <c r="J107" s="18" t="b">
@@ -4892,13 +4908,13 @@
       <c r="F108" s="10">
         <v>13073.3</v>
       </c>
-      <c r="G108" s="10">
+      <c r="G108" s="18">
         <v>18</v>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="25">
         <v>20.000000000000799</v>
       </c>
-      <c r="I108" s="18">
+      <c r="I108" s="25">
         <v>20.000000000000799</v>
       </c>
       <c r="J108" s="18" t="b">
@@ -4932,13 +4948,13 @@
       <c r="F109" s="10">
         <v>13094.1</v>
       </c>
-      <c r="G109" s="10">
+      <c r="G109" s="18">
         <v>21</v>
       </c>
-      <c r="H109" s="10">
+      <c r="H109" s="25">
         <v>15.240384615383819</v>
       </c>
-      <c r="I109" s="18">
+      <c r="I109" s="25">
         <v>15.240384615383819</v>
       </c>
       <c r="J109" s="18" t="b">
@@ -4972,13 +4988,13 @@
       <c r="F110" s="10">
         <v>13115.2</v>
       </c>
-      <c r="G110" s="10">
+      <c r="G110" s="18">
         <v>21</v>
       </c>
-      <c r="H110" s="10">
+      <c r="H110" s="25">
         <v>15.66350710900447</v>
       </c>
-      <c r="I110" s="18">
+      <c r="I110" s="25">
         <v>15.66350710900447</v>
       </c>
       <c r="J110" s="18" t="b">
@@ -5012,13 +5028,13 @@
       <c r="F111" s="10">
         <v>13132.3</v>
       </c>
-      <c r="G111" s="10">
+      <c r="G111" s="18">
         <v>17</v>
       </c>
-      <c r="H111" s="10">
+      <c r="H111" s="25">
         <v>10.84795321637519</v>
       </c>
-      <c r="I111" s="18">
+      <c r="I111" s="25">
         <v>10.84795321637519</v>
       </c>
       <c r="J111" s="18" t="b">
@@ -5052,13 +5068,13 @@
       <c r="F112" s="10">
         <v>13143.6</v>
       </c>
-      <c r="G112" s="10">
-        <v>11</v>
-      </c>
-      <c r="H112" s="10">
+      <c r="G112" s="18">
+        <v>11</v>
+      </c>
+      <c r="H112" s="25">
         <v>18.584070796458381</v>
       </c>
-      <c r="I112" s="18">
+      <c r="I112" s="25">
         <v>18.584070796458381</v>
       </c>
       <c r="J112" s="18" t="b">
@@ -5092,13 +5108,13 @@
       <c r="F113" s="10">
         <v>13157.8</v>
       </c>
-      <c r="G113" s="10">
+      <c r="G113" s="18">
         <v>14</v>
       </c>
-      <c r="H113" s="10">
+      <c r="H113" s="25">
         <v>15.88028169014207</v>
       </c>
-      <c r="I113" s="18">
+      <c r="I113" s="25">
         <v>15.88028169014207</v>
       </c>
       <c r="J113" s="18" t="b">
@@ -5132,13 +5148,13 @@
       <c r="F114" s="10">
         <v>13164.2</v>
       </c>
-      <c r="G114" s="10">
+      <c r="G114" s="18">
         <v>6</v>
       </c>
-      <c r="H114" s="10">
+      <c r="H114" s="25">
         <v>29.531249999993289</v>
       </c>
-      <c r="I114" s="18">
+      <c r="I114" s="25">
         <v>29.531249999993289</v>
       </c>
       <c r="J114" s="18" t="b">
@@ -5172,13 +5188,13 @@
       <c r="F115" s="10">
         <v>13178.4</v>
       </c>
-      <c r="G115" s="10">
+      <c r="G115" s="18">
         <v>14</v>
       </c>
-      <c r="H115" s="10">
+      <c r="H115" s="25">
         <v>16.830985915494249</v>
       </c>
-      <c r="I115" s="18">
+      <c r="I115" s="25">
         <v>16.830985915494249</v>
       </c>
       <c r="J115" s="18" t="b">
@@ -5212,13 +5228,13 @@
       <c r="F116" s="10">
         <v>13196.1</v>
       </c>
-      <c r="G116" s="10">
+      <c r="G116" s="18">
         <v>18</v>
       </c>
-      <c r="H116" s="10">
+      <c r="H116" s="25">
         <v>13.813559322033329</v>
       </c>
-      <c r="I116" s="18">
+      <c r="I116" s="25">
         <v>13.813559322033329</v>
       </c>
       <c r="J116" s="18" t="b">
@@ -5252,13 +5268,13 @@
       <c r="F117" s="10">
         <v>13214.2</v>
       </c>
-      <c r="G117" s="10">
+      <c r="G117" s="18">
         <v>18</v>
       </c>
-      <c r="H117" s="10">
+      <c r="H117" s="25">
         <v>13.701657458563259</v>
       </c>
-      <c r="I117" s="18">
+      <c r="I117" s="25">
         <v>13.701657458563259</v>
       </c>
       <c r="J117" s="18" t="b">
@@ -5292,13 +5308,13 @@
       <c r="F118" s="10">
         <v>13229.7</v>
       </c>
-      <c r="G118" s="10">
+      <c r="G118" s="18">
         <v>16</v>
       </c>
-      <c r="H118" s="10">
+      <c r="H118" s="25">
         <v>4.387096774193548</v>
       </c>
-      <c r="I118" s="18">
+      <c r="I118" s="25">
         <v>4.387096774193548</v>
       </c>
       <c r="J118" s="18" t="b">
@@ -5332,13 +5348,13 @@
       <c r="F119" s="10">
         <v>13229.8</v>
       </c>
-      <c r="G119" s="10">
-        <v>0</v>
-      </c>
-      <c r="H119" s="10">
+      <c r="G119" s="18">
+        <v>0</v>
+      </c>
+      <c r="H119" s="25">
         <v>1965.000000028595</v>
       </c>
-      <c r="I119" s="18">
+      <c r="I119" s="25">
         <v>0</v>
       </c>
       <c r="J119" s="18" t="b">
@@ -5372,13 +5388,13 @@
       <c r="F120" s="10">
         <v>13247.8</v>
       </c>
-      <c r="G120" s="10">
+      <c r="G120" s="18">
         <v>18</v>
       </c>
-      <c r="H120" s="10">
+      <c r="H120" s="25">
         <v>14.361111111111111</v>
       </c>
-      <c r="I120" s="18">
+      <c r="I120" s="25">
         <v>14.361111111111111</v>
       </c>
       <c r="J120" s="18" t="b">
@@ -5412,13 +5428,13 @@
       <c r="F121" s="10">
         <v>5108.2</v>
       </c>
-      <c r="G121" s="10">
+      <c r="G121" s="18">
         <v>20.8</v>
       </c>
-      <c r="H121" s="10">
+      <c r="H121" s="25">
         <v>6.8027876747190796E-2</v>
       </c>
-      <c r="I121" s="18">
+      <c r="I121" s="25">
         <v>0</v>
       </c>
       <c r="J121" s="18" t="b">
@@ -5456,13 +5472,13 @@
       <c r="F122" s="10">
         <v>5151.3999999999996</v>
       </c>
-      <c r="G122" s="10">
+      <c r="G122" s="18">
         <v>43</v>
       </c>
-      <c r="H122" s="10">
+      <c r="H122" s="25">
         <v>8.1134259259259593</v>
       </c>
-      <c r="I122" s="18">
+      <c r="I122" s="25">
         <v>8.1134259259259593</v>
       </c>
       <c r="J122" s="18" t="b">
@@ -5498,13 +5514,13 @@
       <c r="F123" s="10">
         <v>5172.2</v>
       </c>
-      <c r="G123" s="10">
+      <c r="G123" s="18">
         <v>21</v>
       </c>
-      <c r="H123" s="10">
+      <c r="H123" s="25">
         <v>16.538461538461391</v>
       </c>
-      <c r="I123" s="18">
+      <c r="I123" s="25">
         <v>16.538461538461391</v>
       </c>
       <c r="J123" s="18" t="b">
@@ -5540,13 +5556,13 @@
       <c r="F124" s="10">
         <v>5194.3999999999996</v>
       </c>
-      <c r="G124" s="10">
+      <c r="G124" s="18">
         <v>22</v>
       </c>
-      <c r="H124" s="10">
+      <c r="H124" s="25">
         <v>15.337837837837959</v>
       </c>
-      <c r="I124" s="18">
+      <c r="I124" s="25">
         <v>15.337837837837959</v>
       </c>
       <c r="J124" s="18" t="b">
@@ -5582,13 +5598,13 @@
       <c r="F125" s="10">
         <v>5216</v>
       </c>
-      <c r="G125" s="10">
+      <c r="G125" s="18">
         <v>22</v>
       </c>
-      <c r="H125" s="10">
+      <c r="H125" s="25">
         <v>11.36574074074055</v>
       </c>
-      <c r="I125" s="18">
+      <c r="I125" s="25">
         <v>11.36574074074055</v>
       </c>
       <c r="J125" s="18" t="b">
@@ -5624,13 +5640,13 @@
       <c r="F126" s="10">
         <v>5238.1000000000004</v>
       </c>
-      <c r="G126" s="10">
+      <c r="G126" s="18">
         <v>22</v>
       </c>
-      <c r="H126" s="10">
+      <c r="H126" s="25">
         <v>15.45248868778255</v>
       </c>
-      <c r="I126" s="18">
+      <c r="I126" s="25">
         <v>15.45248868778255</v>
       </c>
       <c r="J126" s="18" t="b">
@@ -5666,13 +5682,13 @@
       <c r="F127" s="10">
         <v>5260.5</v>
       </c>
-      <c r="G127" s="10">
+      <c r="G127" s="18">
         <v>22</v>
       </c>
-      <c r="H127" s="10">
+      <c r="H127" s="25">
         <v>15.758928571428831</v>
       </c>
-      <c r="I127" s="18">
+      <c r="I127" s="25">
         <v>15.758928571428831</v>
       </c>
       <c r="J127" s="18" t="b">
@@ -5708,13 +5724,13 @@
       <c r="F128" s="10">
         <v>5282.4</v>
       </c>
-      <c r="G128" s="10">
+      <c r="G128" s="18">
         <v>22</v>
       </c>
-      <c r="H128" s="10">
+      <c r="H128" s="25">
         <v>16.073059360730859</v>
       </c>
-      <c r="I128" s="18">
+      <c r="I128" s="25">
         <v>16.073059360730859</v>
       </c>
       <c r="J128" s="18" t="b">
@@ -5750,13 +5766,13 @@
       <c r="F129" s="10">
         <v>5304.2</v>
       </c>
-      <c r="G129" s="10">
+      <c r="G129" s="18">
         <v>22</v>
       </c>
-      <c r="H129" s="10">
+      <c r="H129" s="25">
         <v>15.18348623853198</v>
       </c>
-      <c r="I129" s="18">
+      <c r="I129" s="25">
         <v>15.18348623853198</v>
       </c>
       <c r="J129" s="18" t="b">
@@ -5792,13 +5808,13 @@
       <c r="F130" s="10">
         <v>5327.1</v>
       </c>
-      <c r="G130" s="10">
+      <c r="G130" s="18">
         <v>23</v>
       </c>
-      <c r="H130" s="10">
+      <c r="H130" s="25">
         <v>15.56768558951928</v>
       </c>
-      <c r="I130" s="18">
+      <c r="I130" s="25">
         <v>15.56768558951928</v>
       </c>
       <c r="J130" s="18" t="b">
@@ -5834,13 +5850,13 @@
       <c r="F131" s="10">
         <v>5349.2</v>
       </c>
-      <c r="G131" s="10">
+      <c r="G131" s="18">
         <v>22</v>
       </c>
-      <c r="H131" s="10">
+      <c r="H131" s="25">
         <v>14.72850678733068</v>
       </c>
-      <c r="I131" s="18">
+      <c r="I131" s="25">
         <v>14.72850678733068</v>
       </c>
       <c r="J131" s="18" t="b">
@@ -5876,13 +5892,13 @@
       <c r="F132" s="10">
         <v>5361</v>
       </c>
-      <c r="G132" s="10">
+      <c r="G132" s="18">
         <v>12</v>
       </c>
-      <c r="H132" s="10">
+      <c r="H132" s="25">
         <v>16.99152542372855</v>
       </c>
-      <c r="I132" s="18">
+      <c r="I132" s="25">
         <v>16.99152542372855</v>
       </c>
       <c r="J132" s="18" t="b">
@@ -5918,13 +5934,13 @@
       <c r="F133" s="10">
         <v>5384.2</v>
       </c>
-      <c r="G133" s="10">
+      <c r="G133" s="18">
         <v>23</v>
       </c>
-      <c r="H133" s="10">
+      <c r="H133" s="25">
         <v>15.237068965517359</v>
       </c>
-      <c r="I133" s="18">
+      <c r="I133" s="25">
         <v>15.237068965517359</v>
       </c>
       <c r="J133" s="18" t="b">
@@ -5960,13 +5976,13 @@
       <c r="F134" s="10">
         <v>5403</v>
       </c>
-      <c r="G134" s="10">
+      <c r="G134" s="18">
         <v>19</v>
       </c>
-      <c r="H134" s="10">
+      <c r="H134" s="25">
         <v>16.11702127659559</v>
       </c>
-      <c r="I134" s="18">
+      <c r="I134" s="25">
         <v>16.11702127659559</v>
       </c>
       <c r="J134" s="18" t="b">
@@ -6002,13 +6018,13 @@
       <c r="F135" s="10">
         <v>5440.1</v>
       </c>
-      <c r="G135" s="10">
+      <c r="G135" s="18">
         <v>37</v>
       </c>
-      <c r="H135" s="10">
+      <c r="H135" s="25">
         <v>8.9353099730457348</v>
       </c>
-      <c r="I135" s="18">
+      <c r="I135" s="25">
         <v>8.9353099730457348</v>
       </c>
       <c r="J135" s="18" t="b">
@@ -6044,13 +6060,13 @@
       <c r="F136" s="10">
         <v>5548.2</v>
       </c>
-      <c r="G136" s="10">
+      <c r="G136" s="18">
         <v>108</v>
       </c>
-      <c r="H136" s="10">
+      <c r="H136" s="25">
         <v>2.8815911193339652</v>
       </c>
-      <c r="I136" s="18">
+      <c r="I136" s="25">
         <v>0</v>
       </c>
       <c r="J136" s="18" t="b">
@@ -6088,9 +6104,9 @@
       <c r="F137" s="10">
         <v>5479.1</v>
       </c>
-      <c r="G137" s="10"/>
-      <c r="H137" s="10"/>
-      <c r="I137" s="18">
+      <c r="G137" s="18"/>
+      <c r="H137" s="25"/>
+      <c r="I137" s="25">
         <v>0</v>
       </c>
       <c r="J137" s="18" t="b">
@@ -6126,13 +6142,13 @@
       <c r="F138" s="10">
         <v>5500</v>
       </c>
-      <c r="G138" s="10">
+      <c r="G138" s="18">
         <v>21</v>
       </c>
-      <c r="H138" s="10">
+      <c r="H138" s="25">
         <v>16.17224880382803</v>
       </c>
-      <c r="I138" s="18">
+      <c r="I138" s="25">
         <v>16.17224880382803</v>
       </c>
       <c r="J138" s="18" t="b">
@@ -6168,13 +6184,13 @@
       <c r="F139" s="10">
         <v>5522.5</v>
       </c>
-      <c r="G139" s="10">
+      <c r="G139" s="18">
         <v>23</v>
       </c>
-      <c r="H139" s="10">
+      <c r="H139" s="25">
         <v>15.31111111111111</v>
       </c>
-      <c r="I139" s="18">
+      <c r="I139" s="25">
         <v>15.31111111111111</v>
       </c>
       <c r="J139" s="18" t="b">
@@ -6210,13 +6226,13 @@
       <c r="F140" s="10">
         <v>5564</v>
       </c>
-      <c r="G140" s="10">
+      <c r="G140" s="18">
         <v>42</v>
       </c>
-      <c r="H140" s="10">
+      <c r="H140" s="25">
         <v>8</v>
       </c>
-      <c r="I140" s="18">
+      <c r="I140" s="25">
         <v>8</v>
       </c>
       <c r="J140" s="18" t="b">
@@ -6252,11 +6268,11 @@
       <c r="F141" s="10">
         <v>5564</v>
       </c>
-      <c r="G141" s="10">
-        <v>0</v>
-      </c>
-      <c r="H141" s="10"/>
-      <c r="I141" s="18">
+      <c r="G141" s="18">
+        <v>0</v>
+      </c>
+      <c r="H141" s="25"/>
+      <c r="I141" s="25">
         <v>0</v>
       </c>
       <c r="J141" s="18" t="b">
@@ -6292,13 +6308,13 @@
       <c r="F142" s="10">
         <v>5583.3</v>
       </c>
-      <c r="G142" s="10">
+      <c r="G142" s="18">
         <v>19</v>
       </c>
-      <c r="H142" s="10">
+      <c r="H142" s="25">
         <v>17.02072538860088</v>
       </c>
-      <c r="I142" s="18">
+      <c r="I142" s="25">
         <v>17.02072538860088</v>
       </c>
       <c r="J142" s="18" t="b">
@@ -6334,13 +6350,13 @@
       <c r="F143" s="10">
         <v>5606.1</v>
       </c>
-      <c r="G143" s="10">
+      <c r="G143" s="18">
         <v>23</v>
       </c>
-      <c r="H143" s="10">
+      <c r="H143" s="25">
         <v>15.1315789473683</v>
       </c>
-      <c r="I143" s="18">
+      <c r="I143" s="25">
         <v>15.1315789473683</v>
       </c>
       <c r="J143" s="18" t="b">
@@ -6376,13 +6392,13 @@
       <c r="F144" s="10">
         <v>5625</v>
       </c>
-      <c r="G144" s="10">
+      <c r="G144" s="18">
         <v>19</v>
       </c>
-      <c r="H144" s="10">
+      <c r="H144" s="25">
         <v>16.587301587301901</v>
       </c>
-      <c r="I144" s="18">
+      <c r="I144" s="25">
         <v>16.587301587301901</v>
       </c>
       <c r="J144" s="18" t="b">
@@ -6418,13 +6434,13 @@
       <c r="F145" s="10">
         <v>5645.3</v>
       </c>
-      <c r="G145" s="10">
+      <c r="G145" s="18">
         <v>20</v>
       </c>
-      <c r="H145" s="10">
+      <c r="H145" s="25">
         <v>17.019704433497381</v>
       </c>
-      <c r="I145" s="18">
+      <c r="I145" s="25">
         <v>17.019704433497381</v>
       </c>
       <c r="J145" s="18" t="b">
@@ -6460,13 +6476,13 @@
       <c r="F146" s="10">
         <v>5665.3</v>
       </c>
-      <c r="G146" s="10">
+      <c r="G146" s="18">
         <v>20</v>
       </c>
-      <c r="H146" s="10">
+      <c r="H146" s="25">
         <v>14.725</v>
       </c>
-      <c r="I146" s="18">
+      <c r="I146" s="25">
         <v>14.725</v>
       </c>
       <c r="J146" s="18" t="b">
@@ -6502,13 +6518,13 @@
       <c r="F147" s="10">
         <v>5684.1</v>
       </c>
-      <c r="G147" s="10">
+      <c r="G147" s="18">
         <v>19</v>
       </c>
-      <c r="H147" s="10">
+      <c r="H147" s="25">
         <v>14.680851063829641</v>
       </c>
-      <c r="I147" s="18">
+      <c r="I147" s="25">
         <v>14.680851063829641</v>
       </c>
       <c r="J147" s="18" t="b">
@@ -6544,13 +6560,13 @@
       <c r="F148" s="10">
         <v>5704.4</v>
       </c>
-      <c r="G148" s="10">
+      <c r="G148" s="18">
         <v>20</v>
       </c>
-      <c r="H148" s="10">
+      <c r="H148" s="25">
         <v>16.206896551724721</v>
       </c>
-      <c r="I148" s="18">
+      <c r="I148" s="25">
         <v>16.206896551724721</v>
       </c>
       <c r="J148" s="18" t="b">
@@ -6586,13 +6602,13 @@
       <c r="F149" s="10">
         <v>5726.4</v>
       </c>
-      <c r="G149" s="10">
+      <c r="G149" s="18">
         <v>22</v>
       </c>
-      <c r="H149" s="10">
+      <c r="H149" s="25">
         <v>14.09090909090909</v>
       </c>
-      <c r="I149" s="18">
+      <c r="I149" s="25">
         <v>14.09090909090909</v>
       </c>
       <c r="J149" s="18" t="b">
@@ -6628,13 +6644,13 @@
       <c r="F150" s="10">
         <v>5745.1</v>
       </c>
-      <c r="G150" s="10">
+      <c r="G150" s="18">
         <v>19</v>
       </c>
-      <c r="H150" s="10">
+      <c r="H150" s="25">
         <v>15.026737967913849</v>
       </c>
-      <c r="I150" s="18">
+      <c r="I150" s="25">
         <v>15.026737967913849</v>
       </c>
       <c r="J150" s="18" t="b">
@@ -6670,13 +6686,13 @@
       <c r="F151" s="10">
         <v>5760.2</v>
       </c>
-      <c r="G151" s="10">
+      <c r="G151" s="18">
         <v>15</v>
       </c>
-      <c r="H151" s="10">
+      <c r="H151" s="25">
         <v>15.86092715231845</v>
       </c>
-      <c r="I151" s="18">
+      <c r="I151" s="25">
         <v>15.86092715231845</v>
       </c>
       <c r="J151" s="18" t="b">
@@ -6712,13 +6728,13 @@
       <c r="F152" s="10">
         <v>5782</v>
       </c>
-      <c r="G152" s="10">
+      <c r="G152" s="18">
         <v>22</v>
       </c>
-      <c r="H152" s="10">
+      <c r="H152" s="25">
         <v>14.95412844036685</v>
       </c>
-      <c r="I152" s="18">
+      <c r="I152" s="25">
         <v>14.95412844036685</v>
       </c>
       <c r="J152" s="18" t="b">
@@ -6754,13 +6770,13 @@
       <c r="F153" s="10">
         <v>5798.4</v>
       </c>
-      <c r="G153" s="10">
+      <c r="G153" s="18">
         <v>16</v>
       </c>
-      <c r="H153" s="10">
+      <c r="H153" s="25">
         <v>17.89634146341503</v>
       </c>
-      <c r="I153" s="18">
+      <c r="I153" s="25">
         <v>17.89634146341503</v>
       </c>
       <c r="J153" s="18" t="b">
@@ -6796,13 +6812,13 @@
       <c r="F154" s="10">
         <v>4942.6000000000004</v>
       </c>
-      <c r="G154" s="10">
+      <c r="G154" s="18">
         <v>43</v>
       </c>
-      <c r="H154" s="10">
+      <c r="H154" s="25">
         <v>7.64</v>
       </c>
-      <c r="I154" s="18">
+      <c r="I154" s="25">
         <v>7.64</v>
       </c>
       <c r="J154" s="18" t="b">
@@ -6838,13 +6854,13 @@
       <c r="F155" s="10">
         <v>4966</v>
       </c>
-      <c r="G155" s="10">
+      <c r="G155" s="18">
         <v>23</v>
       </c>
-      <c r="H155" s="10">
+      <c r="H155" s="25">
         <v>14.102564102564321</v>
       </c>
-      <c r="I155" s="18">
+      <c r="I155" s="25">
         <v>14.102564102564321</v>
       </c>
       <c r="J155" s="18" t="b">
@@ -6880,13 +6896,13 @@
       <c r="F156" s="10">
         <v>4986.7</v>
       </c>
-      <c r="G156" s="10">
+      <c r="G156" s="18">
         <v>21</v>
       </c>
-      <c r="H156" s="10">
+      <c r="H156" s="25">
         <v>15.70048309178758</v>
       </c>
-      <c r="I156" s="18">
+      <c r="I156" s="25">
         <v>15.70048309178758</v>
       </c>
       <c r="J156" s="18" t="b">
@@ -6922,13 +6938,13 @@
       <c r="F157" s="10">
         <v>5008</v>
       </c>
-      <c r="G157" s="10">
+      <c r="G157" s="18">
         <v>21</v>
       </c>
-      <c r="H157" s="10">
+      <c r="H157" s="25">
         <v>15.375586854459961</v>
       </c>
-      <c r="I157" s="18">
+      <c r="I157" s="25">
         <v>15.375586854459961</v>
       </c>
       <c r="J157" s="18" t="b">
@@ -6964,13 +6980,13 @@
       <c r="F158" s="10">
         <v>5026.5</v>
       </c>
-      <c r="G158" s="10">
+      <c r="G158" s="18">
         <v>19</v>
       </c>
-      <c r="H158" s="10">
+      <c r="H158" s="25">
         <v>17.216216216216221</v>
       </c>
-      <c r="I158" s="18">
+      <c r="I158" s="25">
         <v>17.216216216216221</v>
       </c>
       <c r="J158" s="18" t="b">
@@ -7006,13 +7022,13 @@
       <c r="F159" s="10">
         <v>5043.2</v>
       </c>
-      <c r="G159" s="10">
+      <c r="G159" s="18">
         <v>17</v>
       </c>
-      <c r="H159" s="10">
+      <c r="H159" s="25">
         <v>17.395209580838511</v>
       </c>
-      <c r="I159" s="18">
+      <c r="I159" s="25">
         <v>17.395209580838511</v>
       </c>
       <c r="J159" s="18" t="b">
@@ -7048,13 +7064,13 @@
       <c r="F160" s="10">
         <v>5051.8999999999996</v>
       </c>
-      <c r="G160" s="10">
+      <c r="G160" s="18">
         <v>9</v>
       </c>
-      <c r="H160" s="10">
+      <c r="H160" s="25">
         <v>18.793103448276259</v>
       </c>
-      <c r="I160" s="18">
+      <c r="I160" s="25">
         <v>18.793103448276259</v>
       </c>
       <c r="J160" s="18" t="b">
@@ -7090,13 +7106,13 @@
       <c r="F161" s="10">
         <v>5069.6000000000004</v>
       </c>
-      <c r="G161" s="10">
+      <c r="G161" s="18">
         <v>18</v>
       </c>
-      <c r="H161" s="10">
+      <c r="H161" s="25">
         <v>17.68361581920831</v>
       </c>
-      <c r="I161" s="18">
+      <c r="I161" s="25">
         <v>17.68361581920831</v>
       </c>
       <c r="J161" s="18" t="b">
@@ -7132,13 +7148,13 @@
       <c r="F162" s="10">
         <v>5086</v>
       </c>
-      <c r="G162" s="10">
+      <c r="G162" s="18">
         <v>16</v>
       </c>
-      <c r="H162" s="10">
+      <c r="H162" s="25">
         <v>17.835365853658931</v>
       </c>
-      <c r="I162" s="18">
+      <c r="I162" s="25">
         <v>17.835365853658931</v>
       </c>
       <c r="J162" s="18" t="b">
@@ -7174,13 +7190,13 @@
       <c r="F163" s="10">
         <v>5105.5</v>
       </c>
-      <c r="G163" s="10">
+      <c r="G163" s="18">
         <v>20</v>
       </c>
-      <c r="H163" s="10">
+      <c r="H163" s="25">
         <v>16.794871794871799</v>
       </c>
-      <c r="I163" s="18">
+      <c r="I163" s="25">
         <v>16.794871794871799</v>
       </c>
       <c r="J163" s="18" t="b">
@@ -7216,13 +7232,13 @@
       <c r="F164" s="10">
         <v>5122.3999999999996</v>
       </c>
-      <c r="G164" s="10">
+      <c r="G164" s="18">
         <v>17</v>
       </c>
-      <c r="H164" s="10">
+      <c r="H164" s="25">
         <v>18.90532544378739</v>
       </c>
-      <c r="I164" s="18">
+      <c r="I164" s="25">
         <v>18.90532544378739</v>
       </c>
       <c r="J164" s="18" t="b">
@@ -7258,13 +7274,13 @@
       <c r="F165" s="10">
         <v>5138.3</v>
       </c>
-      <c r="G165" s="10">
+      <c r="G165" s="18">
         <v>16</v>
       </c>
-      <c r="H165" s="10">
+      <c r="H165" s="25">
         <v>20.157232704401821</v>
       </c>
-      <c r="I165" s="18">
+      <c r="I165" s="25">
         <v>20.157232704401821</v>
       </c>
       <c r="J165" s="18" t="b">
@@ -7300,13 +7316,13 @@
       <c r="F166" s="10">
         <v>5150.6000000000004</v>
       </c>
-      <c r="G166" s="10">
+      <c r="G166" s="18">
         <v>12</v>
       </c>
-      <c r="H166" s="10">
+      <c r="H166" s="25">
         <v>20.731707317072861</v>
       </c>
-      <c r="I166" s="18">
+      <c r="I166" s="25">
         <v>20.731707317072861</v>
       </c>
       <c r="J166" s="18" t="b">
@@ -7342,13 +7358,13 @@
       <c r="F167" s="10">
         <v>5160.6000000000004</v>
       </c>
-      <c r="G167" s="10">
+      <c r="G167" s="18">
         <v>10</v>
       </c>
-      <c r="H167" s="10">
+      <c r="H167" s="25">
         <v>18.75</v>
       </c>
-      <c r="I167" s="18">
+      <c r="I167" s="25">
         <v>18.75</v>
       </c>
       <c r="J167" s="18" t="b">
@@ -7384,13 +7400,13 @@
       <c r="F168" s="10">
         <v>5175.1000000000004</v>
       </c>
-      <c r="G168" s="10">
+      <c r="G168" s="18">
         <v>15</v>
       </c>
-      <c r="H168" s="10">
+      <c r="H168" s="25">
         <v>19.517241379310349</v>
       </c>
-      <c r="I168" s="18">
+      <c r="I168" s="25">
         <v>19.517241379310349</v>
       </c>
       <c r="J168" s="18" t="b">
@@ -7426,13 +7442,13 @@
       <c r="F169" s="10">
         <v>5175.2</v>
       </c>
-      <c r="G169" s="10">
-        <v>0</v>
-      </c>
-      <c r="H169" s="10">
+      <c r="G169" s="18">
+        <v>0</v>
+      </c>
+      <c r="H169" s="25">
         <v>365.00000000199179</v>
       </c>
-      <c r="I169" s="18">
+      <c r="I169" s="25">
         <v>0</v>
       </c>
       <c r="J169" s="18" t="b">
@@ -7468,13 +7484,13 @@
       <c r="F170" s="10">
         <v>5195.8</v>
       </c>
-      <c r="G170" s="10">
+      <c r="G170" s="18">
         <v>21</v>
       </c>
-      <c r="H170" s="10">
+      <c r="H170" s="25">
         <v>15.582524271844379</v>
       </c>
-      <c r="I170" s="18">
+      <c r="I170" s="25">
         <v>15.582524271844379</v>
       </c>
       <c r="J170" s="18" t="b">
@@ -7510,13 +7526,13 @@
       <c r="F171" s="10">
         <v>5213.7</v>
       </c>
-      <c r="G171" s="10">
+      <c r="G171" s="18">
         <v>18</v>
       </c>
-      <c r="H171" s="10">
+      <c r="H171" s="25">
         <v>15.391061452514281</v>
       </c>
-      <c r="I171" s="18">
+      <c r="I171" s="25">
         <v>15.391061452514281</v>
       </c>
       <c r="J171" s="18" t="b">
@@ -7552,13 +7568,13 @@
       <c r="F172" s="10">
         <v>5234.8999999999996</v>
       </c>
-      <c r="G172" s="10">
+      <c r="G172" s="18">
         <v>21</v>
       </c>
-      <c r="H172" s="10">
+      <c r="H172" s="25">
         <v>15.424528301886919</v>
       </c>
-      <c r="I172" s="18">
+      <c r="I172" s="25">
         <v>15.424528301886919</v>
       </c>
       <c r="J172" s="18" t="b">
@@ -7594,13 +7610,13 @@
       <c r="F173" s="10">
         <v>5255.9</v>
       </c>
-      <c r="G173" s="10">
+      <c r="G173" s="18">
         <v>21</v>
       </c>
-      <c r="H173" s="10">
+      <c r="H173" s="25">
         <v>14.28571428571429</v>
       </c>
-      <c r="I173" s="18">
+      <c r="I173" s="25">
         <v>14.28571428571429</v>
       </c>
       <c r="J173" s="18" t="b">
@@ -7636,13 +7652,13 @@
       <c r="F174" s="10">
         <v>5273.1</v>
       </c>
-      <c r="G174" s="10">
+      <c r="G174" s="18">
         <v>17</v>
       </c>
-      <c r="H174" s="10">
+      <c r="H174" s="25">
         <v>16.162790697673731</v>
       </c>
-      <c r="I174" s="18">
+      <c r="I174" s="25">
         <v>16.162790697673731</v>
       </c>
       <c r="J174" s="18" t="b">
@@ -7678,13 +7694,13 @@
       <c r="F175" s="10">
         <v>5293.6</v>
       </c>
-      <c r="G175" s="10">
+      <c r="G175" s="18">
         <v>21</v>
       </c>
-      <c r="H175" s="10">
+      <c r="H175" s="25">
         <v>15.170731707317071</v>
       </c>
-      <c r="I175" s="18">
+      <c r="I175" s="25">
         <v>15.170731707317071</v>
       </c>
       <c r="J175" s="18" t="b">
@@ -7720,13 +7736,13 @@
       <c r="F176" s="10">
         <v>5310.2</v>
       </c>
-      <c r="G176" s="10">
+      <c r="G176" s="18">
         <v>17</v>
       </c>
-      <c r="H176" s="10">
+      <c r="H176" s="25">
         <v>16.746987951807782</v>
       </c>
-      <c r="I176" s="18">
+      <c r="I176" s="25">
         <v>16.746987951807782</v>
       </c>
       <c r="J176" s="18" t="b">
@@ -7762,13 +7778,13 @@
       <c r="F177" s="10">
         <v>5330.9</v>
       </c>
-      <c r="G177" s="10">
+      <c r="G177" s="18">
         <v>21</v>
       </c>
-      <c r="H177" s="10">
+      <c r="H177" s="25">
         <v>15.7971014492755</v>
       </c>
-      <c r="I177" s="18">
+      <c r="I177" s="25">
         <v>15.7971014492755</v>
       </c>
       <c r="J177" s="18" t="b">
@@ -7804,13 +7820,13 @@
       <c r="F178" s="10">
         <v>5351.6</v>
       </c>
-      <c r="G178" s="10">
+      <c r="G178" s="18">
         <v>21</v>
       </c>
-      <c r="H178" s="10">
+      <c r="H178" s="25">
         <v>15.821256038646791</v>
       </c>
-      <c r="I178" s="18">
+      <c r="I178" s="25">
         <v>15.821256038646791</v>
       </c>
       <c r="J178" s="18" t="b">
@@ -7846,13 +7862,13 @@
       <c r="F179" s="10">
         <v>5369.2</v>
       </c>
-      <c r="G179" s="10">
+      <c r="G179" s="18">
         <v>18</v>
       </c>
-      <c r="H179" s="10">
+      <c r="H179" s="25">
         <v>16.193181818182321</v>
       </c>
-      <c r="I179" s="18">
+      <c r="I179" s="25">
         <v>16.193181818182321</v>
       </c>
       <c r="J179" s="18" t="b">
@@ -7888,13 +7904,13 @@
       <c r="F180" s="10">
         <v>5390.8</v>
       </c>
-      <c r="G180" s="10">
+      <c r="G180" s="18">
         <v>22</v>
       </c>
-      <c r="H180" s="10">
+      <c r="H180" s="25">
         <v>15.185185185184929</v>
       </c>
-      <c r="I180" s="18">
+      <c r="I180" s="25">
         <v>15.185185185184929</v>
       </c>
       <c r="J180" s="18" t="b">
@@ -7930,13 +7946,13 @@
       <c r="F181" s="10">
         <v>5416.5</v>
       </c>
-      <c r="G181" s="10">
+      <c r="G181" s="18">
         <v>26</v>
       </c>
-      <c r="H181" s="10">
+      <c r="H181" s="25">
         <v>12.76264591439698</v>
       </c>
-      <c r="I181" s="18">
+      <c r="I181" s="25">
         <v>12.76264591439698</v>
       </c>
       <c r="J181" s="18" t="b">
@@ -7972,13 +7988,13 @@
       <c r="F182" s="10">
         <v>5441.8</v>
       </c>
-      <c r="G182" s="10">
+      <c r="G182" s="18">
         <v>25</v>
       </c>
-      <c r="H182" s="10">
+      <c r="H182" s="25">
         <v>13.06324110671927</v>
       </c>
-      <c r="I182" s="18">
+      <c r="I182" s="25">
         <v>13.06324110671927</v>
       </c>
       <c r="J182" s="18" t="b">
@@ -8014,13 +8030,13 @@
       <c r="F183" s="10">
         <v>5470.1</v>
       </c>
-      <c r="G183" s="10">
+      <c r="G183" s="18">
         <v>28</v>
       </c>
-      <c r="H183" s="10">
+      <c r="H183" s="25">
         <v>11.537102473498161</v>
       </c>
-      <c r="I183" s="18">
+      <c r="I183" s="25">
         <v>11.537102473498161</v>
       </c>
       <c r="J183" s="18" t="b">
@@ -8056,13 +8072,13 @@
       <c r="F184" s="10">
         <v>5494.2</v>
       </c>
-      <c r="G184" s="10">
+      <c r="G184" s="18">
         <v>24</v>
       </c>
-      <c r="H184" s="10">
+      <c r="H184" s="25">
         <v>13.07053941908743</v>
       </c>
-      <c r="I184" s="18">
+      <c r="I184" s="25">
         <v>13.07053941908743</v>
       </c>
       <c r="J184" s="18" t="b">
@@ -8098,13 +8114,13 @@
       <c r="F185" s="10">
         <v>5519.6</v>
       </c>
-      <c r="G185" s="10">
+      <c r="G185" s="18">
         <v>25</v>
       </c>
-      <c r="H185" s="10">
+      <c r="H185" s="25">
         <v>12.933070866141451</v>
       </c>
-      <c r="I185" s="18">
+      <c r="I185" s="25">
         <v>12.933070866141451</v>
       </c>
       <c r="J185" s="18" t="b">
@@ -8140,13 +8156,13 @@
       <c r="F186" s="10">
         <v>5541.8</v>
       </c>
-      <c r="G186" s="10">
+      <c r="G186" s="18">
         <v>22</v>
       </c>
-      <c r="H186" s="10">
+      <c r="H186" s="25">
         <v>13.96396396396408</v>
       </c>
-      <c r="I186" s="18">
+      <c r="I186" s="25">
         <v>13.96396396396408</v>
       </c>
       <c r="J186" s="18" t="b">
@@ -8182,13 +8198,13 @@
       <c r="F187" s="10">
         <v>5562.3</v>
       </c>
-      <c r="G187" s="10">
+      <c r="G187" s="18">
         <v>21</v>
       </c>
-      <c r="H187" s="10">
+      <c r="H187" s="25">
         <v>15.463414634146339</v>
       </c>
-      <c r="I187" s="18">
+      <c r="I187" s="25">
         <v>15.463414634146339</v>
       </c>
       <c r="J187" s="18" t="b">
@@ -8224,13 +8240,13 @@
       <c r="F188" s="10">
         <v>5585</v>
       </c>
-      <c r="G188" s="10">
+      <c r="G188" s="18">
         <v>23</v>
       </c>
-      <c r="H188" s="10">
+      <c r="H188" s="25">
         <v>14.581497797356951</v>
       </c>
-      <c r="I188" s="18">
+      <c r="I188" s="25">
         <v>14.581497797356951</v>
       </c>
       <c r="J188" s="18" t="b">
@@ -8266,13 +8282,13 @@
       <c r="F189" s="10">
         <v>5608</v>
       </c>
-      <c r="G189" s="10">
+      <c r="G189" s="18">
         <v>23</v>
       </c>
-      <c r="H189" s="10">
+      <c r="H189" s="25">
         <v>14.260869565217391</v>
       </c>
-      <c r="I189" s="18">
+      <c r="I189" s="25">
         <v>14.260869565217391</v>
       </c>
       <c r="J189" s="18" t="b">
@@ -8308,13 +8324,13 @@
       <c r="F190" s="10">
         <v>5630.4</v>
       </c>
-      <c r="G190" s="10">
+      <c r="G190" s="18">
         <v>22</v>
       </c>
-      <c r="H190" s="10">
+      <c r="H190" s="25">
         <v>14.55357142857167</v>
       </c>
-      <c r="I190" s="18">
+      <c r="I190" s="25">
         <v>14.55357142857167</v>
       </c>
       <c r="J190" s="18" t="b">
@@ -8350,13 +8366,13 @@
       <c r="F191" s="10">
         <v>5650.7</v>
       </c>
-      <c r="G191" s="10">
+      <c r="G191" s="18">
         <v>20</v>
       </c>
-      <c r="H191" s="10">
+      <c r="H191" s="25">
         <v>14.60591133004913</v>
       </c>
-      <c r="I191" s="18">
+      <c r="I191" s="25">
         <v>14.60591133004913</v>
       </c>
       <c r="J191" s="18" t="b">
@@ -8392,13 +8408,13 @@
       <c r="F192" s="10">
         <v>5671.7</v>
       </c>
-      <c r="G192" s="10">
+      <c r="G192" s="18">
         <v>21</v>
       </c>
-      <c r="H192" s="10">
+      <c r="H192" s="25">
         <v>14.452380952380951</v>
       </c>
-      <c r="I192" s="18">
+      <c r="I192" s="25">
         <v>14.452380952380951</v>
       </c>
       <c r="J192" s="18" t="b">
@@ -8434,13 +8450,13 @@
       <c r="F193" s="10">
         <v>1121.5</v>
       </c>
-      <c r="G193" s="10">
+      <c r="G193" s="18">
         <v>36.299999999999997</v>
       </c>
-      <c r="H193" s="10">
+      <c r="H193" s="25">
         <v>15.375586854459961</v>
       </c>
-      <c r="I193" s="18">
+      <c r="I193" s="25">
         <v>15.375586854459961</v>
       </c>
       <c r="J193" s="18" t="b">
@@ -8476,13 +8492,13 @@
       <c r="F194" s="10">
         <v>1161.2</v>
       </c>
-      <c r="G194" s="10">
+      <c r="G194" s="18">
         <v>40</v>
       </c>
-      <c r="H194" s="10">
+      <c r="H194" s="25">
         <v>8.7783375314861356</v>
       </c>
-      <c r="I194" s="18">
+      <c r="I194" s="25">
         <v>8.7783375314861356</v>
       </c>
       <c r="J194" s="18" t="b">
@@ -8518,13 +8534,13 @@
       <c r="F195" s="10">
         <v>1183.3</v>
       </c>
-      <c r="G195" s="10">
+      <c r="G195" s="18">
         <v>22</v>
       </c>
-      <c r="H195" s="10">
+      <c r="H195" s="25">
         <v>11.877828054298689</v>
       </c>
-      <c r="I195" s="18">
+      <c r="I195" s="25">
         <v>11.877828054298689</v>
       </c>
       <c r="J195" s="18" t="b">
@@ -8560,13 +8576,13 @@
       <c r="F196" s="10">
         <v>1202.2</v>
       </c>
-      <c r="G196" s="10">
+      <c r="G196" s="18">
         <v>19</v>
       </c>
-      <c r="H196" s="10">
+      <c r="H196" s="25">
         <v>25.05291005290993</v>
       </c>
-      <c r="I196" s="18">
+      <c r="I196" s="25">
         <v>25.05291005290993</v>
       </c>
       <c r="J196" s="18" t="b">
@@ -8602,13 +8618,13 @@
       <c r="F197" s="10">
         <v>1225.2</v>
       </c>
-      <c r="G197" s="10">
+      <c r="G197" s="18">
         <v>23</v>
       </c>
-      <c r="H197" s="10">
+      <c r="H197" s="25">
         <v>12.32608695652174</v>
       </c>
-      <c r="I197" s="18">
+      <c r="I197" s="25">
         <v>12.32608695652174</v>
       </c>
       <c r="J197" s="18" t="b">
@@ -8644,13 +8660,13 @@
       <c r="F198" s="10">
         <v>1245.5</v>
       </c>
-      <c r="G198" s="10">
+      <c r="G198" s="18">
         <v>20</v>
       </c>
-      <c r="H198" s="10">
+      <c r="H198" s="25">
         <v>13.423645320197069</v>
       </c>
-      <c r="I198" s="18">
+      <c r="I198" s="25">
         <v>13.423645320197069</v>
       </c>
       <c r="J198" s="18" t="b">
@@ -8686,13 +8702,13 @@
       <c r="F199" s="10">
         <v>1270.5999999999999</v>
       </c>
-      <c r="G199" s="10">
+      <c r="G199" s="18">
         <v>25</v>
       </c>
-      <c r="H199" s="10">
+      <c r="H199" s="25">
         <v>9.5617529880478429</v>
       </c>
-      <c r="I199" s="18">
+      <c r="I199" s="25">
         <v>9.5617529880478429</v>
       </c>
       <c r="J199" s="18" t="b">
@@ -8728,13 +8744,13 @@
       <c r="F200" s="10">
         <v>1292.7</v>
       </c>
-      <c r="G200" s="10">
+      <c r="G200" s="18">
         <v>22</v>
       </c>
-      <c r="H200" s="10">
+      <c r="H200" s="25">
         <v>13.574660633484079</v>
       </c>
-      <c r="I200" s="18">
+      <c r="I200" s="25">
         <v>13.574660633484079</v>
       </c>
       <c r="J200" s="18" t="b">
@@ -8770,13 +8786,13 @@
       <c r="F201" s="10">
         <v>1321.9</v>
       </c>
-      <c r="G201" s="10">
+      <c r="G201" s="18">
         <v>29</v>
       </c>
-      <c r="H201" s="10">
+      <c r="H201" s="25">
         <v>8.7499999999999858</v>
       </c>
-      <c r="I201" s="18">
+      <c r="I201" s="25">
         <v>8.7499999999999858</v>
       </c>
       <c r="J201" s="18" t="b">
@@ -8812,13 +8828,13 @@
       <c r="F202" s="10">
         <v>1350.2</v>
       </c>
-      <c r="G202" s="10">
+      <c r="G202" s="18">
         <v>28</v>
       </c>
-      <c r="H202" s="10">
+      <c r="H202" s="25">
         <v>8.7632508833922405</v>
       </c>
-      <c r="I202" s="18">
+      <c r="I202" s="25">
         <v>8.7632508833922405</v>
       </c>
       <c r="J202" s="18" t="b">
@@ -8854,13 +8870,13 @@
       <c r="F203" s="10">
         <v>1375.5</v>
       </c>
-      <c r="G203" s="10">
+      <c r="G203" s="18">
         <v>25</v>
       </c>
-      <c r="H203" s="10">
+      <c r="H203" s="25">
         <v>9.3873517786561429</v>
       </c>
-      <c r="I203" s="18">
+      <c r="I203" s="25">
         <v>9.3873517786561429</v>
       </c>
       <c r="J203" s="18" t="b">
@@ -8896,13 +8912,13 @@
       <c r="F204" s="10">
         <v>1408</v>
       </c>
-      <c r="G204" s="10">
+      <c r="G204" s="18">
         <v>33</v>
       </c>
-      <c r="H204" s="10">
+      <c r="H204" s="25">
         <v>8.4615384615384617</v>
       </c>
-      <c r="I204" s="18">
+      <c r="I204" s="25">
         <v>8.4615384615384617</v>
       </c>
       <c r="J204" s="18" t="b">
@@ -8938,13 +8954,13 @@
       <c r="F205" s="10">
         <v>1427.9</v>
       </c>
-      <c r="G205" s="10">
+      <c r="G205" s="18">
         <v>20</v>
       </c>
-      <c r="H205" s="10">
+      <c r="H205" s="25">
         <v>14.673366834170791</v>
       </c>
-      <c r="I205" s="18">
+      <c r="I205" s="25">
         <v>14.673366834170791</v>
       </c>
       <c r="J205" s="18" t="b">
@@ -8980,13 +8996,13 @@
       <c r="F206" s="10">
         <v>1459.5</v>
       </c>
-      <c r="G206" s="10">
+      <c r="G206" s="18">
         <v>32</v>
       </c>
-      <c r="H206" s="10">
+      <c r="H206" s="25">
         <v>9.2088607594936978</v>
       </c>
-      <c r="I206" s="18">
+      <c r="I206" s="25">
         <v>9.2088607594936978</v>
       </c>
       <c r="J206" s="18" t="b">
@@ -9022,13 +9038,13 @@
       <c r="F207" s="10">
         <v>1485.8</v>
       </c>
-      <c r="G207" s="10">
+      <c r="G207" s="18">
         <v>26</v>
       </c>
-      <c r="H207" s="10">
+      <c r="H207" s="25">
         <v>8.7642585551330949</v>
       </c>
-      <c r="I207" s="18">
+      <c r="I207" s="25">
         <v>8.7642585551330949</v>
       </c>
       <c r="J207" s="18" t="b">
@@ -9064,13 +9080,13 @@
       <c r="F208" s="10">
         <v>1516.2</v>
       </c>
-      <c r="G208" s="10">
+      <c r="G208" s="18">
         <v>30</v>
       </c>
-      <c r="H208" s="10">
+      <c r="H208" s="25">
         <v>10.641447368421019</v>
       </c>
-      <c r="I208" s="18">
+      <c r="I208" s="25">
         <v>10.641447368421019</v>
       </c>
       <c r="J208" s="18" t="b">
@@ -9106,13 +9122,13 @@
       <c r="F209" s="10">
         <v>1543.3</v>
       </c>
-      <c r="G209" s="10">
-        <v>27</v>
-      </c>
-      <c r="H209" s="10">
+      <c r="G209" s="18">
+        <v>27</v>
+      </c>
+      <c r="H209" s="25">
         <v>9.9077490774908075</v>
       </c>
-      <c r="I209" s="18">
+      <c r="I209" s="25">
         <v>9.9077490774908075</v>
       </c>
       <c r="J209" s="18" t="b">
@@ -9148,13 +9164,13 @@
       <c r="F210" s="10">
         <v>1565.8</v>
       </c>
-      <c r="G210" s="10">
+      <c r="G210" s="18">
         <v>23</v>
       </c>
-      <c r="H210" s="10">
+      <c r="H210" s="25">
         <v>13.62222222222222</v>
       </c>
-      <c r="I210" s="18">
+      <c r="I210" s="25">
         <v>13.62222222222222</v>
       </c>
       <c r="J210" s="18" t="b">
@@ -9190,13 +9206,13 @@
       <c r="F211" s="10">
         <v>1590.4</v>
       </c>
-      <c r="G211" s="10">
+      <c r="G211" s="18">
         <v>25</v>
       </c>
-      <c r="H211" s="10">
+      <c r="H211" s="25">
         <v>10.67073170731701</v>
       </c>
-      <c r="I211" s="18">
+      <c r="I211" s="25">
         <v>10.67073170731701</v>
       </c>
       <c r="J211" s="18" t="b">
@@ -9232,13 +9248,13 @@
       <c r="F212" s="10">
         <v>1615</v>
       </c>
-      <c r="G212" s="10">
+      <c r="G212" s="18">
         <v>25</v>
       </c>
-      <c r="H212" s="10">
+      <c r="H212" s="25">
         <v>11.524390243902481</v>
       </c>
-      <c r="I212" s="18">
+      <c r="I212" s="25">
         <v>11.524390243902481</v>
       </c>
       <c r="J212" s="18" t="b">
@@ -9274,13 +9290,13 @@
       <c r="F213" s="10">
         <v>1637.1</v>
       </c>
-      <c r="G213" s="10">
+      <c r="G213" s="18">
         <v>22</v>
       </c>
-      <c r="H213" s="10">
+      <c r="H213" s="25">
         <v>14.298642533936709</v>
       </c>
-      <c r="I213" s="18">
+      <c r="I213" s="25">
         <v>14.298642533936709</v>
       </c>
       <c r="J213" s="18" t="b">
@@ -9316,13 +9332,13 @@
       <c r="F214" s="10">
         <v>1660.2</v>
       </c>
-      <c r="G214" s="10">
+      <c r="G214" s="18">
         <v>23</v>
       </c>
-      <c r="H214" s="10">
+      <c r="H214" s="25">
         <v>12.29437229437222</v>
       </c>
-      <c r="I214" s="18">
+      <c r="I214" s="25">
         <v>12.29437229437222</v>
       </c>
       <c r="J214" s="18" t="b">
@@ -9358,13 +9374,13 @@
       <c r="F215" s="10">
         <v>1678.3</v>
       </c>
-      <c r="G215" s="10">
+      <c r="G215" s="18">
         <v>18</v>
       </c>
-      <c r="H215" s="10">
+      <c r="H215" s="25">
         <v>15.33149171270726</v>
       </c>
-      <c r="I215" s="18">
+      <c r="I215" s="25">
         <v>15.33149171270726</v>
       </c>
       <c r="J215" s="18" t="b">
@@ -9400,13 +9416,13 @@
       <c r="F216" s="10">
         <v>1697.1</v>
       </c>
-      <c r="G216" s="10">
+      <c r="G216" s="18">
         <v>19</v>
       </c>
-      <c r="H216" s="10">
+      <c r="H216" s="25">
         <v>14.0957446808511</v>
       </c>
-      <c r="I216" s="18">
+      <c r="I216" s="25">
         <v>14.0957446808511</v>
       </c>
       <c r="J216" s="18" t="b">
@@ -9442,13 +9458,13 @@
       <c r="F217" s="10">
         <v>1936.76</v>
       </c>
-      <c r="G217" s="10">
+      <c r="G217" s="18">
         <v>240</v>
       </c>
-      <c r="H217" s="10">
+      <c r="H217" s="25">
         <v>1.2079612784778431</v>
       </c>
-      <c r="I217" s="18">
+      <c r="I217" s="25">
         <v>0</v>
       </c>
       <c r="J217" s="18" t="b">
@@ -9486,9 +9502,9 @@
       <c r="F218" s="10">
         <v>1750.3</v>
       </c>
-      <c r="G218" s="10"/>
-      <c r="H218" s="10"/>
-      <c r="I218" s="18">
+      <c r="G218" s="18"/>
+      <c r="H218" s="25"/>
+      <c r="I218" s="25">
         <v>0</v>
       </c>
       <c r="J218" s="18" t="b">
@@ -9524,13 +9540,13 @@
       <c r="F219" s="10">
         <v>1777.8</v>
       </c>
-      <c r="G219" s="10">
+      <c r="G219" s="18">
         <v>28</v>
       </c>
-      <c r="H219" s="10">
+      <c r="H219" s="25">
         <v>11.23636363636364</v>
       </c>
-      <c r="I219" s="18">
+      <c r="I219" s="25">
         <v>11.23636363636364</v>
       </c>
       <c r="J219" s="18" t="b">
@@ -9566,13 +9582,13 @@
       <c r="F220" s="10">
         <v>1807.5</v>
       </c>
-      <c r="G220" s="10">
+      <c r="G220" s="18">
         <v>30</v>
       </c>
-      <c r="H220" s="10">
+      <c r="H220" s="25">
         <v>3.3670033670033621E-2</v>
       </c>
-      <c r="I220" s="18">
+      <c r="I220" s="25">
         <v>0</v>
       </c>
       <c r="J220" s="18" t="b">
@@ -9610,11 +9626,11 @@
       <c r="F221" s="10">
         <v>1807.5</v>
       </c>
-      <c r="G221" s="10">
-        <v>0</v>
-      </c>
-      <c r="H221" s="10"/>
-      <c r="I221" s="18">
+      <c r="G221" s="18">
+        <v>0</v>
+      </c>
+      <c r="H221" s="25"/>
+      <c r="I221" s="25">
         <v>0</v>
       </c>
       <c r="J221" s="18" t="b">
@@ -9650,13 +9666,13 @@
       <c r="F222" s="10">
         <v>1826.2</v>
       </c>
-      <c r="G222" s="10">
+      <c r="G222" s="18">
         <v>19</v>
       </c>
-      <c r="H222" s="10">
+      <c r="H222" s="25">
         <v>2.673796791443844E-2</v>
       </c>
-      <c r="I222" s="18">
+      <c r="I222" s="25">
         <v>0</v>
       </c>
       <c r="J222" s="18" t="b">
@@ -9694,13 +9710,13 @@
       <c r="F223" s="10">
         <v>1941.6</v>
       </c>
-      <c r="G223" s="10">
+      <c r="G223" s="18">
         <v>115</v>
       </c>
-      <c r="H223" s="10">
+      <c r="H223" s="25">
         <v>2.6473136915078022</v>
       </c>
-      <c r="I223" s="18">
+      <c r="I223" s="25">
         <v>0</v>
       </c>
       <c r="J223" s="18" t="b">
@@ -9738,13 +9754,13 @@
       <c r="F224" s="10">
         <v>1962.1</v>
       </c>
-      <c r="G224" s="10">
+      <c r="G224" s="18">
         <v>21</v>
       </c>
-      <c r="H224" s="10">
+      <c r="H224" s="25">
         <v>14.585365853658541</v>
       </c>
-      <c r="I224" s="18">
+      <c r="I224" s="25">
         <v>14.585365853658541</v>
       </c>
       <c r="J224" s="18" t="b">
@@ -9780,13 +9796,13 @@
       <c r="F225" s="10">
         <v>1980.5</v>
       </c>
-      <c r="G225" s="10">
+      <c r="G225" s="18">
         <v>18</v>
       </c>
-      <c r="H225" s="10">
+      <c r="H225" s="25">
         <v>13.94021739130428</v>
       </c>
-      <c r="I225" s="18">
+      <c r="I225" s="25">
         <v>13.94021739130428</v>
       </c>
       <c r="J225" s="18" t="b">
@@ -9822,13 +9838,13 @@
       <c r="F226" s="10">
         <v>5733.4</v>
       </c>
-      <c r="G226" s="10">
+      <c r="G226" s="18">
         <v>23</v>
       </c>
-      <c r="H226" s="10">
+      <c r="H226" s="25">
         <v>12.628</v>
       </c>
-      <c r="I226" s="18">
+      <c r="I226" s="25">
         <v>12.628</v>
       </c>
       <c r="J226" s="18" t="b">
@@ -9864,13 +9880,13 @@
       <c r="F227" s="10">
         <v>5756.7</v>
       </c>
-      <c r="G227" s="10">
+      <c r="G227" s="18">
         <v>23</v>
       </c>
-      <c r="H227" s="10">
+      <c r="H227" s="25">
         <v>12.811158798283159</v>
       </c>
-      <c r="I227" s="18">
+      <c r="I227" s="25">
         <v>12.811158798283159</v>
       </c>
       <c r="J227" s="18" t="b">
@@ -9906,13 +9922,13 @@
       <c r="F228" s="10">
         <v>5782.3</v>
       </c>
-      <c r="G228" s="10">
+      <c r="G228" s="18">
         <v>26</v>
       </c>
-      <c r="H228" s="10">
+      <c r="H228" s="25">
         <v>12.890624999999821</v>
       </c>
-      <c r="I228" s="18">
+      <c r="I228" s="25">
         <v>12.890624999999821</v>
       </c>
       <c r="J228" s="18" t="b">
@@ -9948,13 +9964,13 @@
       <c r="F229" s="10">
         <v>5804.5</v>
       </c>
-      <c r="G229" s="10">
+      <c r="G229" s="18">
         <v>22</v>
       </c>
-      <c r="H229" s="10">
+      <c r="H229" s="25">
         <v>12.207207207207309</v>
       </c>
-      <c r="I229" s="18">
+      <c r="I229" s="25">
         <v>12.207207207207309</v>
       </c>
       <c r="J229" s="18" t="b">
@@ -9990,13 +10006,13 @@
       <c r="F230" s="10">
         <v>5830.6</v>
       </c>
-      <c r="G230" s="10">
+      <c r="G230" s="18">
         <v>26</v>
       </c>
-      <c r="H230" s="10">
+      <c r="H230" s="25">
         <v>12.394636015325499</v>
       </c>
-      <c r="I230" s="18">
+      <c r="I230" s="25">
         <v>12.394636015325499</v>
       </c>
       <c r="J230" s="18" t="b">
@@ -10032,13 +10048,13 @@
       <c r="F231" s="10">
         <v>5850.3</v>
       </c>
-      <c r="G231" s="10">
+      <c r="G231" s="18">
         <v>20</v>
       </c>
-      <c r="H231" s="10">
+      <c r="H231" s="25">
         <v>12.690355329949361</v>
       </c>
-      <c r="I231" s="18">
+      <c r="I231" s="25">
         <v>12.690355329949361</v>
       </c>
       <c r="J231" s="18" t="b">
@@ -10074,13 +10090,13 @@
       <c r="F232" s="10">
         <v>5878.9</v>
       </c>
-      <c r="G232" s="10">
+      <c r="G232" s="18">
         <v>29</v>
       </c>
-      <c r="H232" s="10">
+      <c r="H232" s="25">
         <v>11.1888111888114</v>
       </c>
-      <c r="I232" s="18">
+      <c r="I232" s="25">
         <v>11.1888111888114</v>
       </c>
       <c r="J232" s="18" t="b">
@@ -10116,13 +10132,13 @@
       <c r="F233" s="10">
         <v>5904.3</v>
       </c>
-      <c r="G233" s="10">
+      <c r="G233" s="18">
         <v>25</v>
       </c>
-      <c r="H233" s="10">
+      <c r="H233" s="25">
         <v>11.929133858267461</v>
       </c>
-      <c r="I233" s="18">
+      <c r="I233" s="25">
         <v>11.929133858267461</v>
       </c>
       <c r="J233" s="18" t="b">
@@ -10158,13 +10174,13 @@
       <c r="F234" s="10">
         <v>5927.7</v>
       </c>
-      <c r="G234" s="10">
+      <c r="G234" s="18">
         <v>23</v>
       </c>
-      <c r="H234" s="10">
+      <c r="H234" s="25">
         <v>12.564102564102759</v>
       </c>
-      <c r="I234" s="18">
+      <c r="I234" s="25">
         <v>12.564102564102759</v>
       </c>
       <c r="J234" s="18" t="b">
@@ -10200,13 +10216,13 @@
       <c r="F235" s="10">
         <v>5949.5</v>
       </c>
-      <c r="G235" s="10">
+      <c r="G235" s="18">
         <v>22</v>
       </c>
-      <c r="H235" s="10">
+      <c r="H235" s="25">
         <v>12.29357798165127</v>
       </c>
-      <c r="I235" s="18">
+      <c r="I235" s="25">
         <v>12.29357798165127</v>
       </c>
       <c r="J235" s="18" t="b">
@@ -10242,13 +10258,13 @@
       <c r="F236" s="10">
         <v>5973</v>
       </c>
-      <c r="G236" s="10">
+      <c r="G236" s="18">
         <v>24</v>
       </c>
-      <c r="H236" s="10">
+      <c r="H236" s="25">
         <v>13.87234042553191</v>
       </c>
-      <c r="I236" s="18">
+      <c r="I236" s="25">
         <v>13.87234042553191</v>
       </c>
       <c r="J236" s="18" t="b">
@@ -10284,13 +10300,13 @@
       <c r="F237" s="10">
         <v>5997.2</v>
       </c>
-      <c r="G237" s="10">
+      <c r="G237" s="18">
         <v>24</v>
       </c>
-      <c r="H237" s="10">
+      <c r="H237" s="25">
         <v>11.859504132231489</v>
       </c>
-      <c r="I237" s="18">
+      <c r="I237" s="25">
         <v>11.859504132231489</v>
       </c>
       <c r="J237" s="18" t="b">
@@ -10326,13 +10342,13 @@
       <c r="F238" s="10">
         <v>6019.4</v>
       </c>
-      <c r="G238" s="10">
+      <c r="G238" s="18">
         <v>22</v>
       </c>
-      <c r="H238" s="10">
+      <c r="H238" s="25">
         <v>13.130630630630741</v>
       </c>
-      <c r="I238" s="18">
+      <c r="I238" s="25">
         <v>13.130630630630741</v>
       </c>
       <c r="J238" s="18" t="b">
@@ -10368,13 +10384,13 @@
       <c r="F239" s="10">
         <v>6044.6</v>
       </c>
-      <c r="G239" s="10">
+      <c r="G239" s="18">
         <v>25</v>
       </c>
-      <c r="H239" s="10">
+      <c r="H239" s="25">
         <v>10.714285714285401</v>
       </c>
-      <c r="I239" s="18">
+      <c r="I239" s="25">
         <v>10.714285714285401</v>
       </c>
       <c r="J239" s="18" t="b">
@@ -10410,13 +10426,13 @@
       <c r="F240" s="10">
         <v>6066.7</v>
       </c>
-      <c r="G240" s="10">
+      <c r="G240" s="18">
         <v>22</v>
       </c>
-      <c r="H240" s="10">
+      <c r="H240" s="25">
         <v>14.1855203619913</v>
       </c>
-      <c r="I240" s="18">
+      <c r="I240" s="25">
         <v>14.1855203619913</v>
       </c>
       <c r="J240" s="18" t="b">
@@ -10452,13 +10468,13 @@
       <c r="F241" s="10">
         <v>6095.4</v>
       </c>
-      <c r="G241" s="10">
+      <c r="G241" s="18">
         <v>29</v>
       </c>
-      <c r="H241" s="10">
+      <c r="H241" s="25">
         <v>11.60278745644607</v>
       </c>
-      <c r="I241" s="18">
+      <c r="I241" s="25">
         <v>11.60278745644607</v>
       </c>
       <c r="J241" s="18" t="b">
@@ -10494,13 +10510,13 @@
       <c r="F242" s="10">
         <v>6120.9</v>
       </c>
-      <c r="G242" s="10">
+      <c r="G242" s="18">
         <v>26</v>
       </c>
-      <c r="H242" s="10">
+      <c r="H242" s="25">
         <v>12.098039215686271</v>
       </c>
-      <c r="I242" s="18">
+      <c r="I242" s="25">
         <v>12.098039215686271</v>
       </c>
       <c r="J242" s="18" t="b">
@@ -10536,13 +10552,13 @@
       <c r="F243" s="10">
         <v>6147.2</v>
       </c>
-      <c r="G243" s="10">
+      <c r="G243" s="18">
         <v>26</v>
       </c>
-      <c r="H243" s="10">
+      <c r="H243" s="25">
         <v>12.319391634980899</v>
       </c>
-      <c r="I243" s="18">
+      <c r="I243" s="25">
         <v>12.319391634980899</v>
       </c>
       <c r="J243" s="18" t="b">
@@ -10578,13 +10594,13 @@
       <c r="F244" s="10">
         <v>6226.5</v>
       </c>
-      <c r="G244" s="10">
+      <c r="G244" s="18">
         <v>79</v>
       </c>
-      <c r="H244" s="10">
+      <c r="H244" s="25">
         <v>3.9785624211853632</v>
       </c>
-      <c r="I244" s="18">
+      <c r="I244" s="25">
         <v>3.9785624211853632</v>
       </c>
       <c r="J244" s="18" t="b">
@@ -10620,13 +10636,13 @@
       <c r="F245" s="10">
         <v>6250.7</v>
       </c>
-      <c r="G245" s="10">
+      <c r="G245" s="18">
         <v>24</v>
       </c>
-      <c r="H245" s="10">
+      <c r="H245" s="25">
         <v>13.842975206611669</v>
       </c>
-      <c r="I245" s="18">
+      <c r="I245" s="25">
         <v>13.842975206611669</v>
       </c>
       <c r="J245" s="18" t="b">
@@ -10662,13 +10678,13 @@
       <c r="F246" s="10">
         <v>6277.2</v>
       </c>
-      <c r="G246" s="10">
-        <v>27</v>
-      </c>
-      <c r="H246" s="10">
+      <c r="G246" s="18">
+        <v>27</v>
+      </c>
+      <c r="H246" s="25">
         <v>12.67924528301887</v>
       </c>
-      <c r="I246" s="18">
+      <c r="I246" s="25">
         <v>12.67924528301887</v>
       </c>
       <c r="J246" s="18" t="b">
@@ -10704,13 +10720,13 @@
       <c r="F247" s="10">
         <v>6303</v>
       </c>
-      <c r="G247" s="10">
+      <c r="G247" s="18">
         <v>26</v>
       </c>
-      <c r="H247" s="10">
+      <c r="H247" s="25">
         <v>12.48062015503867</v>
       </c>
-      <c r="I247" s="18">
+      <c r="I247" s="25">
         <v>12.48062015503867</v>
       </c>
       <c r="J247" s="18" t="b">
@@ -10746,13 +10762,13 @@
       <c r="F248" s="10">
         <v>6329.5</v>
       </c>
-      <c r="G248" s="10">
-        <v>27</v>
-      </c>
-      <c r="H248" s="10">
+      <c r="G248" s="18">
+        <v>27</v>
+      </c>
+      <c r="H248" s="25">
         <v>12.188679245283019</v>
       </c>
-      <c r="I248" s="18">
+      <c r="I248" s="25">
         <v>12.188679245283019</v>
       </c>
       <c r="J248" s="18" t="b">
@@ -10788,13 +10804,13 @@
       <c r="F249" s="10">
         <v>6355.2</v>
       </c>
-      <c r="G249" s="10">
+      <c r="G249" s="18">
         <v>26</v>
       </c>
-      <c r="H249" s="10">
+      <c r="H249" s="25">
         <v>13.171206225681029</v>
       </c>
-      <c r="I249" s="18">
+      <c r="I249" s="25">
         <v>13.171206225681029</v>
       </c>
       <c r="J249" s="18" t="b">
@@ -10830,13 +10846,13 @@
       <c r="F250" s="10">
         <v>6379.9</v>
       </c>
-      <c r="G250" s="10">
+      <c r="G250" s="18">
         <v>25</v>
       </c>
-      <c r="H250" s="10">
+      <c r="H250" s="25">
         <v>12.935222672064871</v>
       </c>
-      <c r="I250" s="18">
+      <c r="I250" s="25">
         <v>12.935222672064871</v>
       </c>
       <c r="J250" s="18" t="b">
@@ -10872,13 +10888,13 @@
       <c r="F251" s="10">
         <v>6402.1</v>
       </c>
-      <c r="G251" s="10">
+      <c r="G251" s="18">
         <v>22</v>
       </c>
-      <c r="H251" s="10">
+      <c r="H251" s="25">
         <v>15.135135135134639</v>
       </c>
-      <c r="I251" s="18">
+      <c r="I251" s="25">
         <v>15.135135135134639</v>
       </c>
       <c r="J251" s="18" t="b">
@@ -10914,13 +10930,13 @@
       <c r="F252" s="10">
         <v>15668</v>
       </c>
-      <c r="G252" s="10">
+      <c r="G252" s="18">
         <v>20</v>
       </c>
-      <c r="H252" s="10">
+      <c r="H252" s="25">
         <v>15.5</v>
       </c>
-      <c r="I252" s="18">
+      <c r="I252" s="25">
         <v>15.5</v>
       </c>
       <c r="J252" s="18" t="b">
@@ -10956,13 +10972,13 @@
       <c r="F253" s="10">
         <v>15685</v>
       </c>
-      <c r="G253" s="10">
+      <c r="G253" s="18">
         <v>17</v>
       </c>
-      <c r="H253" s="10">
+      <c r="H253" s="25">
         <v>17</v>
       </c>
-      <c r="I253" s="18">
+      <c r="I253" s="25">
         <v>17</v>
       </c>
       <c r="J253" s="18" t="b">
@@ -10998,13 +11014,13 @@
       <c r="F254" s="10">
         <v>15698</v>
       </c>
-      <c r="G254" s="10">
+      <c r="G254" s="18">
         <v>13</v>
       </c>
-      <c r="H254" s="10">
+      <c r="H254" s="25">
         <v>18.03846153846154</v>
       </c>
-      <c r="I254" s="18">
+      <c r="I254" s="25">
         <v>18.03846153846154</v>
       </c>
       <c r="J254" s="18" t="b">
@@ -11040,13 +11056,13 @@
       <c r="F255" s="10">
         <v>15713.4</v>
       </c>
-      <c r="G255" s="10">
+      <c r="G255" s="18">
         <v>15</v>
       </c>
-      <c r="H255" s="10">
+      <c r="H255" s="25">
         <v>15.616883116883489</v>
       </c>
-      <c r="I255" s="18">
+      <c r="I255" s="25">
         <v>15.616883116883489</v>
       </c>
       <c r="J255" s="18" t="b">
@@ -11082,13 +11098,13 @@
       <c r="F256" s="10">
         <v>15731.6</v>
       </c>
-      <c r="G256" s="10">
+      <c r="G256" s="18">
         <v>18</v>
       </c>
-      <c r="H256" s="10">
+      <c r="H256" s="25">
         <v>13.296703296702759</v>
       </c>
-      <c r="I256" s="18">
+      <c r="I256" s="25">
         <v>13.296703296702759</v>
       </c>
       <c r="J256" s="18" t="b">
@@ -11124,13 +11140,13 @@
       <c r="F257" s="10">
         <v>15750.9</v>
       </c>
-      <c r="G257" s="10">
+      <c r="G257" s="18">
         <v>19</v>
       </c>
-      <c r="H257" s="10">
+      <c r="H257" s="25">
         <v>13.21243523316112</v>
       </c>
-      <c r="I257" s="18">
+      <c r="I257" s="25">
         <v>13.21243523316112</v>
       </c>
       <c r="J257" s="18" t="b">
@@ -11166,13 +11182,13 @@
       <c r="F258" s="10">
         <v>15768.4</v>
       </c>
-      <c r="G258" s="10">
+      <c r="G258" s="18">
         <v>18</v>
       </c>
-      <c r="H258" s="10">
+      <c r="H258" s="25">
         <v>14.11428571428571</v>
       </c>
-      <c r="I258" s="18">
+      <c r="I258" s="25">
         <v>14.11428571428571</v>
       </c>
       <c r="J258" s="18" t="b">
@@ -11208,13 +11224,13 @@
       <c r="F259" s="10">
         <v>15784.6</v>
       </c>
-      <c r="G259" s="10">
+      <c r="G259" s="18">
         <v>16</v>
       </c>
-      <c r="H259" s="10">
+      <c r="H259" s="25">
         <v>15.09259259259191</v>
       </c>
-      <c r="I259" s="18">
+      <c r="I259" s="25">
         <v>15.09259259259191</v>
       </c>
       <c r="J259" s="18" t="b">
@@ -11250,13 +11266,13 @@
       <c r="F260" s="10">
         <v>15799.7</v>
       </c>
-      <c r="G260" s="10">
+      <c r="G260" s="18">
         <v>15</v>
       </c>
-      <c r="H260" s="10">
+      <c r="H260" s="25">
         <v>16.026490066224781</v>
       </c>
-      <c r="I260" s="18">
+      <c r="I260" s="25">
         <v>16.026490066224781</v>
       </c>
       <c r="J260" s="18" t="b">
@@ -11292,13 +11308,13 @@
       <c r="F261" s="10">
         <v>15815.9</v>
       </c>
-      <c r="G261" s="10">
+      <c r="G261" s="18">
         <v>16</v>
       </c>
-      <c r="H261" s="10">
+      <c r="H261" s="25">
         <v>12.530864197531709</v>
       </c>
-      <c r="I261" s="18">
+      <c r="I261" s="25">
         <v>12.530864197531709</v>
       </c>
       <c r="J261" s="18" t="b">
@@ -11334,13 +11350,13 @@
       <c r="F262" s="10">
         <v>15834.3</v>
       </c>
-      <c r="G262" s="10">
+      <c r="G262" s="18">
         <v>18</v>
       </c>
-      <c r="H262" s="10">
+      <c r="H262" s="25">
         <v>13.50543478260896</v>
       </c>
-      <c r="I262" s="18">
+      <c r="I262" s="25">
         <v>13.50543478260896</v>
       </c>
       <c r="J262" s="18" t="b">
@@ -11376,13 +11392,13 @@
       <c r="F263" s="10">
         <v>15849.6</v>
       </c>
-      <c r="G263" s="10">
+      <c r="G263" s="18">
         <v>15</v>
       </c>
-      <c r="H263" s="10">
+      <c r="H263" s="25">
         <v>14.215686274508791</v>
       </c>
-      <c r="I263" s="18">
+      <c r="I263" s="25">
         <v>14.215686274508791</v>
       </c>
       <c r="J263" s="18" t="b">
@@ -11418,13 +11434,13 @@
       <c r="F264" s="10">
         <v>15865.7</v>
       </c>
-      <c r="G264" s="10">
+      <c r="G264" s="18">
         <v>16</v>
       </c>
-      <c r="H264" s="10">
+      <c r="H264" s="25">
         <v>14.96894409937854</v>
       </c>
-      <c r="I264" s="18">
+      <c r="I264" s="25">
         <v>14.96894409937854</v>
       </c>
       <c r="J264" s="18" t="b">
@@ -11460,13 +11476,13 @@
       <c r="F265" s="10">
         <v>15878.5</v>
       </c>
-      <c r="G265" s="10">
+      <c r="G265" s="18">
         <v>13</v>
       </c>
-      <c r="H265" s="10">
+      <c r="H265" s="25">
         <v>17.96875000000102</v>
       </c>
-      <c r="I265" s="18">
+      <c r="I265" s="25">
         <v>17.96875000000102</v>
       </c>
       <c r="J265" s="18" t="b">
@@ -11502,13 +11518,13 @@
       <c r="F266" s="10">
         <v>15894.7</v>
       </c>
-      <c r="G266" s="10">
+      <c r="G266" s="18">
         <v>16</v>
       </c>
-      <c r="H266" s="10">
+      <c r="H266" s="25">
         <v>13.98148148148085</v>
       </c>
-      <c r="I266" s="18">
+      <c r="I266" s="25">
         <v>13.98148148148085</v>
       </c>
       <c r="J266" s="18" t="b">
@@ -11544,13 +11560,13 @@
       <c r="F267" s="10">
         <v>15913.9</v>
       </c>
-      <c r="G267" s="10">
+      <c r="G267" s="18">
         <v>19</v>
       </c>
-      <c r="H267" s="10">
+      <c r="H267" s="25">
         <v>13.93229166666746</v>
       </c>
-      <c r="I267" s="18">
+      <c r="I267" s="25">
         <v>13.93229166666746</v>
       </c>
       <c r="J267" s="18" t="b">
@@ -11586,13 +11602,13 @@
       <c r="F268" s="10">
         <v>15926.3</v>
       </c>
-      <c r="G268" s="10">
+      <c r="G268" s="18">
         <v>12</v>
       </c>
-      <c r="H268" s="10">
+      <c r="H268" s="25">
         <v>18.750000000000551</v>
       </c>
-      <c r="I268" s="18">
+      <c r="I268" s="25">
         <v>18.750000000000551</v>
       </c>
       <c r="J268" s="18" t="b">
@@ -11628,9 +11644,9 @@
       <c r="F269" s="10">
         <v>15642.7</v>
       </c>
-      <c r="G269" s="10"/>
-      <c r="H269" s="10"/>
-      <c r="I269" s="18">
+      <c r="G269" s="18"/>
+      <c r="H269" s="25"/>
+      <c r="I269" s="25">
         <v>0</v>
       </c>
       <c r="J269" s="18" t="b">
@@ -11666,13 +11682,13 @@
       <c r="F270" s="10">
         <v>15964.4</v>
       </c>
-      <c r="G270" s="10">
+      <c r="G270" s="18">
         <v>322</v>
       </c>
-      <c r="H270" s="10">
+      <c r="H270" s="25">
         <v>0.98694435809760983</v>
       </c>
-      <c r="I270" s="18">
+      <c r="I270" s="25">
         <v>0</v>
       </c>
       <c r="J270" s="18" t="b">
@@ -11710,13 +11726,13 @@
       <c r="F271" s="10">
         <v>15978.6</v>
       </c>
-      <c r="G271" s="10">
+      <c r="G271" s="18">
         <v>14</v>
       </c>
-      <c r="H271" s="10">
+      <c r="H271" s="25">
         <v>17.11267605633715</v>
       </c>
-      <c r="I271" s="18">
+      <c r="I271" s="25">
         <v>17.11267605633715</v>
       </c>
       <c r="J271" s="18" t="b">
@@ -11752,13 +11768,13 @@
       <c r="F272" s="10">
         <v>15993.2</v>
       </c>
-      <c r="G272" s="10">
+      <c r="G272" s="18">
         <v>15</v>
       </c>
-      <c r="H272" s="10">
+      <c r="H272" s="25">
         <v>16.71232876712287</v>
       </c>
-      <c r="I272" s="18">
+      <c r="I272" s="25">
         <v>16.71232876712287</v>
       </c>
       <c r="J272" s="18" t="b">
@@ -11794,13 +11810,13 @@
       <c r="F273" s="10">
         <v>16007.6</v>
       </c>
-      <c r="G273" s="10">
+      <c r="G273" s="18">
         <v>14</v>
       </c>
-      <c r="H273" s="10">
+      <c r="H273" s="25">
         <v>16.527777777778191</v>
       </c>
-      <c r="I273" s="18">
+      <c r="I273" s="25">
         <v>16.527777777778191</v>
       </c>
       <c r="J273" s="18" t="b">
@@ -11836,13 +11852,13 @@
       <c r="F274" s="10">
         <v>16024</v>
       </c>
-      <c r="G274" s="10">
+      <c r="G274" s="18">
         <v>16</v>
       </c>
-      <c r="H274" s="10">
+      <c r="H274" s="25">
         <v>17.987804878049179</v>
       </c>
-      <c r="I274" s="18">
+      <c r="I274" s="25">
         <v>17.987804878049179</v>
       </c>
       <c r="J274" s="18" t="b">
@@ -11878,13 +11894,13 @@
       <c r="F275" s="10">
         <v>16040.5</v>
       </c>
-      <c r="G275" s="10">
+      <c r="G275" s="18">
         <v>17</v>
       </c>
-      <c r="H275" s="10">
+      <c r="H275" s="25">
         <v>15.878787878787881</v>
       </c>
-      <c r="I275" s="18">
+      <c r="I275" s="25">
         <v>15.878787878787881</v>
       </c>
       <c r="J275" s="18" t="b">
@@ -11920,13 +11936,13 @@
       <c r="F276" s="10">
         <v>16058.3</v>
       </c>
-      <c r="G276" s="10">
+      <c r="G276" s="18">
         <v>18</v>
       </c>
-      <c r="H276" s="10">
+      <c r="H276" s="25">
         <v>17.162921348315312</v>
       </c>
-      <c r="I276" s="18">
+      <c r="I276" s="25">
         <v>17.162921348315312</v>
       </c>
       <c r="J276" s="18" t="b">
@@ -11962,13 +11978,13 @@
       <c r="F277" s="10">
         <v>16073.8</v>
       </c>
-      <c r="G277" s="10">
+      <c r="G277" s="18">
         <v>16</v>
       </c>
-      <c r="H277" s="10">
+      <c r="H277" s="25">
         <v>16.516129032258061</v>
       </c>
-      <c r="I277" s="18">
+      <c r="I277" s="25">
         <v>16.516129032258061</v>
       </c>
       <c r="J277" s="18" t="b">
@@ -12004,13 +12020,13 @@
       <c r="F278" s="10">
         <v>16086.5</v>
       </c>
-      <c r="G278" s="10">
+      <c r="G278" s="18">
         <v>13</v>
       </c>
-      <c r="H278" s="10">
+      <c r="H278" s="25">
         <v>20.551181102361031</v>
       </c>
-      <c r="I278" s="18">
+      <c r="I278" s="25">
         <v>20.551181102361031</v>
       </c>
       <c r="J278" s="18" t="b">
@@ -12046,13 +12062,13 @@
       <c r="F279" s="10">
         <v>16097.4</v>
       </c>
-      <c r="G279" s="10">
-        <v>11</v>
-      </c>
-      <c r="H279" s="10">
+      <c r="G279" s="18">
+        <v>11</v>
+      </c>
+      <c r="H279" s="25">
         <v>22.798165137615442</v>
       </c>
-      <c r="I279" s="18">
+      <c r="I279" s="25">
         <v>22.798165137615442</v>
       </c>
       <c r="J279" s="18" t="b">
@@ -12088,13 +12104,13 @@
       <c r="F280" s="10">
         <v>16109.7</v>
       </c>
-      <c r="G280" s="10">
+      <c r="G280" s="18">
         <v>12</v>
       </c>
-      <c r="H280" s="10">
+      <c r="H280" s="25">
         <v>19.512195121949489</v>
       </c>
-      <c r="I280" s="18">
+      <c r="I280" s="25">
         <v>19.512195121949489</v>
       </c>
       <c r="J280" s="18" t="b">
@@ -12130,13 +12146,13 @@
       <c r="F281" s="10">
         <v>16124.8</v>
       </c>
-      <c r="G281" s="10">
+      <c r="G281" s="18">
         <v>15</v>
       </c>
-      <c r="H281" s="10">
+      <c r="H281" s="25">
         <v>18.410596026491842</v>
       </c>
-      <c r="I281" s="18">
+      <c r="I281" s="25">
         <v>18.410596026491842</v>
       </c>
       <c r="J281" s="18" t="b">
@@ -12172,13 +12188,13 @@
       <c r="F282" s="10">
         <v>16136.3</v>
       </c>
-      <c r="G282" s="10">
+      <c r="G282" s="18">
         <v>12</v>
       </c>
-      <c r="H282" s="10">
+      <c r="H282" s="25">
         <v>19.65217391304348</v>
       </c>
-      <c r="I282" s="18">
+      <c r="I282" s="25">
         <v>19.65217391304348</v>
       </c>
       <c r="J282" s="18" t="b">
@@ -12214,13 +12230,13 @@
       <c r="F283" s="10">
         <v>16149.6</v>
       </c>
-      <c r="G283" s="10">
+      <c r="G283" s="18">
         <v>13</v>
       </c>
-      <c r="H283" s="10">
+      <c r="H283" s="25">
         <v>15.451127819547599</v>
       </c>
-      <c r="I283" s="18">
+      <c r="I283" s="25">
         <v>15.451127819547599</v>
       </c>
       <c r="J283" s="18" t="b">
@@ -12256,13 +12272,13 @@
       <c r="F284" s="10">
         <v>16164.3</v>
       </c>
-      <c r="G284" s="10">
+      <c r="G284" s="18">
         <v>15</v>
       </c>
-      <c r="H284" s="10">
+      <c r="H284" s="25">
         <v>17.108843537416242</v>
       </c>
-      <c r="I284" s="18">
+      <c r="I284" s="25">
         <v>17.108843537416242</v>
       </c>
       <c r="J284" s="18" t="b">
@@ -12298,13 +12314,13 @@
       <c r="F285" s="10">
         <v>16178.7</v>
       </c>
-      <c r="G285" s="10">
+      <c r="G285" s="18">
         <v>14</v>
       </c>
-      <c r="H285" s="10">
+      <c r="H285" s="25">
         <v>16.493055555553891</v>
       </c>
-      <c r="I285" s="18">
+      <c r="I285" s="25">
         <v>16.493055555553891</v>
       </c>
       <c r="J285" s="18" t="b">
@@ -12340,13 +12356,13 @@
       <c r="F286" s="10">
         <v>16193.4</v>
       </c>
-      <c r="G286" s="10">
+      <c r="G286" s="18">
         <v>15</v>
       </c>
-      <c r="H286" s="10">
+      <c r="H286" s="25">
         <v>18.333333333334689</v>
       </c>
-      <c r="I286" s="18">
+      <c r="I286" s="25">
         <v>18.333333333334689</v>
       </c>
       <c r="J286" s="18" t="b">
@@ -12382,13 +12398,13 @@
       <c r="F287" s="10">
         <v>16239.5</v>
       </c>
-      <c r="G287" s="10">
+      <c r="G287" s="18">
         <v>46</v>
       </c>
-      <c r="H287" s="10">
+      <c r="H287" s="25">
         <v>1.572668112798252</v>
       </c>
-      <c r="I287" s="18">
+      <c r="I287" s="25">
         <v>0</v>
       </c>
       <c r="J287" s="18" t="b">
@@ -12426,13 +12442,13 @@
       <c r="F288" s="10">
         <v>16253.9</v>
       </c>
-      <c r="G288" s="10">
+      <c r="G288" s="18">
         <v>14</v>
       </c>
-      <c r="H288" s="10">
+      <c r="H288" s="25">
         <v>0.27777777777778478</v>
       </c>
-      <c r="I288" s="18">
+      <c r="I288" s="25">
         <v>0</v>
       </c>
       <c r="J288" s="18" t="b">
@@ -12470,13 +12486,13 @@
       <c r="F289" s="10">
         <v>16255.2</v>
       </c>
-      <c r="G289" s="10">
+      <c r="G289" s="18">
         <v>1</v>
       </c>
-      <c r="H289" s="10">
+      <c r="H289" s="25">
         <v>123.0769230768198</v>
       </c>
-      <c r="I289" s="18">
+      <c r="I289" s="25">
         <v>0</v>
       </c>
       <c r="J289" s="18" t="b">
@@ -12514,13 +12530,13 @@
       <c r="F290" s="10">
         <v>16264.6</v>
       </c>
-      <c r="G290" s="10">
+      <c r="G290" s="18">
         <v>9</v>
       </c>
-      <c r="H290" s="10">
+      <c r="H290" s="25">
         <v>25.69148936170312</v>
       </c>
-      <c r="I290" s="18">
+      <c r="I290" s="25">
         <v>25.69148936170312</v>
       </c>
       <c r="J290" s="18" t="b">
@@ -12556,13 +12572,13 @@
       <c r="F291" s="10">
         <v>16279.8</v>
       </c>
-      <c r="G291" s="10">
+      <c r="G291" s="18">
         <v>15</v>
       </c>
-      <c r="H291" s="10">
+      <c r="H291" s="25">
         <v>1.842105263158027</v>
       </c>
-      <c r="I291" s="18">
+      <c r="I291" s="25">
         <v>0</v>
       </c>
       <c r="J291" s="18" t="b">
@@ -12600,13 +12616,13 @@
       <c r="F292" s="10">
         <v>16290.5</v>
       </c>
-      <c r="G292" s="10">
-        <v>11</v>
-      </c>
-      <c r="H292" s="10">
+      <c r="G292" s="18">
+        <v>11</v>
+      </c>
+      <c r="H292" s="25">
         <v>28.224299065418641</v>
       </c>
-      <c r="I292" s="18">
+      <c r="I292" s="25">
         <v>28.224299065418641</v>
       </c>
       <c r="J292" s="18" t="b">
@@ -12642,13 +12658,13 @@
       <c r="F293" s="10">
         <v>16305</v>
       </c>
-      <c r="G293" s="10">
+      <c r="G293" s="18">
         <v>15</v>
       </c>
-      <c r="H293" s="10">
+      <c r="H293" s="25">
         <v>3.4482758620689648E-2</v>
       </c>
-      <c r="I293" s="18">
+      <c r="I293" s="25">
         <v>0</v>
       </c>
       <c r="J293" s="18" t="b">
@@ -12686,13 +12702,13 @@
       <c r="F294" s="10">
         <v>16323.8</v>
       </c>
-      <c r="G294" s="10">
+      <c r="G294" s="18">
         <v>19</v>
       </c>
-      <c r="H294" s="10">
+      <c r="H294" s="25">
         <v>2.6595744680852091E-2</v>
       </c>
-      <c r="I294" s="18">
+      <c r="I294" s="25">
         <v>0</v>
       </c>
       <c r="J294" s="18" t="b">
@@ -12730,13 +12746,13 @@
       <c r="F295" s="10">
         <v>16345</v>
       </c>
-      <c r="G295" s="10">
+      <c r="G295" s="18">
         <v>21</v>
       </c>
-      <c r="H295" s="10">
+      <c r="H295" s="25">
         <v>1.9339622641508769</v>
       </c>
-      <c r="I295" s="18">
+      <c r="I295" s="25">
         <v>0</v>
       </c>
       <c r="J295" s="18" t="b">
@@ -12774,13 +12790,13 @@
       <c r="F296" s="10">
         <v>16346</v>
       </c>
-      <c r="G296" s="10">
+      <c r="G296" s="18">
         <v>1</v>
       </c>
-      <c r="H296" s="10">
+      <c r="H296" s="25">
         <v>274</v>
       </c>
-      <c r="I296" s="18">
+      <c r="I296" s="25">
         <v>0</v>
       </c>
       <c r="J296" s="18" t="b">
@@ -12818,13 +12834,13 @@
       <c r="F297" s="10">
         <v>16377</v>
       </c>
-      <c r="G297" s="10">
+      <c r="G297" s="18">
         <v>31</v>
       </c>
-      <c r="H297" s="10">
+      <c r="H297" s="25">
         <v>8.935483870967742</v>
       </c>
-      <c r="I297" s="18">
+      <c r="I297" s="25">
         <v>8.935483870967742</v>
       </c>
       <c r="J297" s="18" t="b">
@@ -12860,13 +12876,13 @@
       <c r="F298" s="10">
         <v>16392.2</v>
       </c>
-      <c r="G298" s="10">
+      <c r="G298" s="18">
         <v>15</v>
       </c>
-      <c r="H298" s="10">
+      <c r="H298" s="25">
         <v>16.15131578947291</v>
       </c>
-      <c r="I298" s="18">
+      <c r="I298" s="25">
         <v>16.15131578947291</v>
       </c>
       <c r="J298" s="18" t="b">
@@ -12902,13 +12918,13 @@
       <c r="F299" s="10">
         <v>16408.8</v>
       </c>
-      <c r="G299" s="10">
+      <c r="G299" s="18">
         <v>17</v>
       </c>
-      <c r="H299" s="10">
+      <c r="H299" s="25">
         <v>16.716867469880981</v>
       </c>
-      <c r="I299" s="18">
+      <c r="I299" s="25">
         <v>16.716867469880981</v>
       </c>
       <c r="J299" s="18" t="b">
@@ -12944,13 +12960,13 @@
       <c r="F300" s="10">
         <v>16419.400000000001</v>
       </c>
-      <c r="G300" s="10">
-        <v>11</v>
-      </c>
-      <c r="H300" s="10">
+      <c r="G300" s="18">
+        <v>11</v>
+      </c>
+      <c r="H300" s="25">
         <v>22.216981132070899</v>
       </c>
-      <c r="I300" s="18">
+      <c r="I300" s="25">
         <v>22.216981132070899</v>
       </c>
       <c r="J300" s="18" t="b">
@@ -12986,13 +13002,13 @@
       <c r="F301" s="10">
         <v>16432.8</v>
       </c>
-      <c r="G301" s="10">
+      <c r="G301" s="18">
         <v>13</v>
       </c>
-      <c r="H301" s="10">
+      <c r="H301" s="25">
         <v>19.029850746271759</v>
       </c>
-      <c r="I301" s="18">
+      <c r="I301" s="25">
         <v>19.029850746271759</v>
       </c>
       <c r="J301" s="18" t="b">
@@ -13028,13 +13044,13 @@
       <c r="F302" s="10">
         <v>11492</v>
       </c>
-      <c r="G302" s="10">
+      <c r="G302" s="18">
         <v>22</v>
       </c>
-      <c r="H302" s="10">
+      <c r="H302" s="25">
         <v>13.659000000000001</v>
       </c>
-      <c r="I302" s="18">
+      <c r="I302" s="25">
         <v>13.659000000000001</v>
       </c>
       <c r="J302" s="18" t="b">
@@ -13070,13 +13086,13 @@
       <c r="F303" s="10">
         <v>11512</v>
       </c>
-      <c r="G303" s="10">
+      <c r="G303" s="18">
         <v>20</v>
       </c>
-      <c r="H303" s="10">
+      <c r="H303" s="25">
         <v>14.175000000000001</v>
       </c>
-      <c r="I303" s="18">
+      <c r="I303" s="25">
         <v>14.175000000000001</v>
       </c>
       <c r="J303" s="18" t="b">
@@ -13112,13 +13128,13 @@
       <c r="F304" s="10">
         <v>11532.2</v>
       </c>
-      <c r="G304" s="10">
+      <c r="G304" s="18">
         <v>20</v>
       </c>
-      <c r="H304" s="10">
+      <c r="H304" s="25">
         <v>14.554455445544029</v>
       </c>
-      <c r="I304" s="18">
+      <c r="I304" s="25">
         <v>14.554455445544029</v>
       </c>
       <c r="J304" s="18" t="b">
@@ -13154,13 +13170,13 @@
       <c r="F305" s="10">
         <v>11550.1</v>
       </c>
-      <c r="G305" s="10">
+      <c r="G305" s="18">
         <v>18</v>
       </c>
-      <c r="H305" s="10">
+      <c r="H305" s="25">
         <v>13.54748603351983</v>
       </c>
-      <c r="I305" s="18">
+      <c r="I305" s="25">
         <v>13.54748603351983</v>
       </c>
       <c r="J305" s="18" t="b">
@@ -13196,13 +13212,13 @@
       <c r="F306" s="10">
         <v>11568.4</v>
       </c>
-      <c r="G306" s="10">
+      <c r="G306" s="18">
         <v>18</v>
       </c>
-      <c r="H306" s="10">
+      <c r="H306" s="25">
         <v>14.78142076502791</v>
       </c>
-      <c r="I306" s="18">
+      <c r="I306" s="25">
         <v>14.78142076502791</v>
       </c>
       <c r="J306" s="18" t="b">
@@ -13238,13 +13254,13 @@
       <c r="F307" s="10">
         <v>11587.6</v>
       </c>
-      <c r="G307" s="10">
+      <c r="G307" s="18">
         <v>19</v>
       </c>
-      <c r="H307" s="10">
+      <c r="H307" s="25">
         <v>14.869791666666099</v>
       </c>
-      <c r="I307" s="18">
+      <c r="I307" s="25">
         <v>14.869791666666099</v>
       </c>
       <c r="J307" s="18" t="b">
@@ -13280,13 +13296,13 @@
       <c r="F308" s="10">
         <v>11608.4</v>
       </c>
-      <c r="G308" s="10">
+      <c r="G308" s="18">
         <v>21</v>
       </c>
-      <c r="H308" s="10">
+      <c r="H308" s="25">
         <v>14.51923076923128</v>
       </c>
-      <c r="I308" s="18">
+      <c r="I308" s="25">
         <v>14.51923076923128</v>
       </c>
       <c r="J308" s="18" t="b">
@@ -13322,13 +13338,13 @@
       <c r="F309" s="10">
         <v>11634</v>
       </c>
-      <c r="G309" s="10">
+      <c r="G309" s="18">
         <v>26</v>
       </c>
-      <c r="H309" s="10">
+      <c r="H309" s="25">
         <v>3.2617187499999538</v>
       </c>
-      <c r="I309" s="18">
+      <c r="I309" s="25">
         <v>3.2617187499999538</v>
       </c>
       <c r="J309" s="18" t="b">
@@ -13364,11 +13380,11 @@
       <c r="F310" s="10">
         <v>11634</v>
       </c>
-      <c r="G310" s="10">
-        <v>0</v>
-      </c>
-      <c r="H310" s="10"/>
-      <c r="I310" s="18">
+      <c r="G310" s="18">
+        <v>0</v>
+      </c>
+      <c r="H310" s="25"/>
+      <c r="I310" s="25">
         <v>0</v>
       </c>
       <c r="J310" s="18" t="b">
@@ -13404,13 +13420,13 @@
       <c r="F311" s="10">
         <v>11654</v>
       </c>
-      <c r="G311" s="10">
+      <c r="G311" s="18">
         <v>20</v>
       </c>
-      <c r="H311" s="10">
+      <c r="H311" s="25">
         <v>15.425000000000001</v>
       </c>
-      <c r="I311" s="18">
+      <c r="I311" s="25">
         <v>15.425000000000001</v>
       </c>
       <c r="J311" s="18" t="b">
@@ -13446,13 +13462,13 @@
       <c r="F312" s="10">
         <v>11671</v>
       </c>
-      <c r="G312" s="10">
+      <c r="G312" s="18">
         <v>17</v>
       </c>
-      <c r="H312" s="10">
+      <c r="H312" s="25">
         <v>15.382352941176469</v>
       </c>
-      <c r="I312" s="18">
+      <c r="I312" s="25">
         <v>15.382352941176469</v>
       </c>
       <c r="J312" s="18" t="b">
@@ -13488,13 +13504,13 @@
       <c r="F313" s="10">
         <v>11691.1</v>
       </c>
-      <c r="G313" s="10">
+      <c r="G313" s="18">
         <v>20</v>
       </c>
-      <c r="H313" s="10">
+      <c r="H313" s="25">
         <v>15.37313432835793</v>
       </c>
-      <c r="I313" s="18">
+      <c r="I313" s="25">
         <v>15.37313432835793</v>
       </c>
       <c r="J313" s="18" t="b">
@@ -13530,13 +13546,13 @@
       <c r="F314" s="10">
         <v>11710.1</v>
       </c>
-      <c r="G314" s="10">
+      <c r="G314" s="18">
         <v>19</v>
       </c>
-      <c r="H314" s="10">
+      <c r="H314" s="25">
         <v>13.289473684210529</v>
       </c>
-      <c r="I314" s="18">
+      <c r="I314" s="25">
         <v>13.289473684210529</v>
       </c>
       <c r="J314" s="18" t="b">
@@ -13572,13 +13588,13 @@
       <c r="F315" s="10">
         <v>11728</v>
       </c>
-      <c r="G315" s="10">
+      <c r="G315" s="18">
         <v>18</v>
       </c>
-      <c r="H315" s="10">
+      <c r="H315" s="25">
         <v>14.32960893854778</v>
       </c>
-      <c r="I315" s="18">
+      <c r="I315" s="25">
         <v>14.32960893854778</v>
       </c>
       <c r="J315" s="18" t="b">
@@ -13614,13 +13630,13 @@
       <c r="F316" s="10">
         <v>11747</v>
       </c>
-      <c r="G316" s="10">
+      <c r="G316" s="18">
         <v>19</v>
       </c>
-      <c r="H316" s="10">
+      <c r="H316" s="25">
         <v>14.236842105263159</v>
       </c>
-      <c r="I316" s="18">
+      <c r="I316" s="25">
         <v>14.236842105263159</v>
       </c>
       <c r="J316" s="18" t="b">
@@ -13656,13 +13672,13 @@
       <c r="F317" s="10">
         <v>11764</v>
       </c>
-      <c r="G317" s="10">
+      <c r="G317" s="18">
         <v>17</v>
       </c>
-      <c r="H317" s="10">
+      <c r="H317" s="25">
         <v>14.882352941176469</v>
       </c>
-      <c r="I317" s="18">
+      <c r="I317" s="25">
         <v>14.882352941176469</v>
       </c>
       <c r="J317" s="18" t="b">
@@ -13698,13 +13714,13 @@
       <c r="F318" s="10">
         <v>11781</v>
       </c>
-      <c r="G318" s="10">
+      <c r="G318" s="18">
         <v>17</v>
       </c>
-      <c r="H318" s="10">
+      <c r="H318" s="25">
         <v>15.382352941176469</v>
       </c>
-      <c r="I318" s="18">
+      <c r="I318" s="25">
         <v>15.382352941176469</v>
       </c>
       <c r="J318" s="18" t="b">
@@ -13740,13 +13756,13 @@
       <c r="F319" s="10">
         <v>11802</v>
       </c>
-      <c r="G319" s="10">
+      <c r="G319" s="18">
         <v>21</v>
       </c>
-      <c r="H319" s="10">
+      <c r="H319" s="25">
         <v>14.071428571428569</v>
       </c>
-      <c r="I319" s="18">
+      <c r="I319" s="25">
         <v>14.071428571428569</v>
       </c>
       <c r="J319" s="18" t="b">
@@ -13782,13 +13798,13 @@
       <c r="F320" s="10">
         <v>11823</v>
       </c>
-      <c r="G320" s="10">
+      <c r="G320" s="18">
         <v>21</v>
       </c>
-      <c r="H320" s="10">
+      <c r="H320" s="25">
         <v>13.857142857142859</v>
       </c>
-      <c r="I320" s="18">
+      <c r="I320" s="25">
         <v>13.857142857142859</v>
       </c>
       <c r="J320" s="18" t="b">
@@ -13824,13 +13840,13 @@
       <c r="F321" s="10">
         <v>11844</v>
       </c>
-      <c r="G321" s="10">
+      <c r="G321" s="18">
         <v>21</v>
       </c>
-      <c r="H321" s="10">
+      <c r="H321" s="25">
         <v>13.047619047619049</v>
       </c>
-      <c r="I321" s="18">
+      <c r="I321" s="25">
         <v>13.047619047619049</v>
       </c>
       <c r="J321" s="18" t="b">
@@ -13866,13 +13882,13 @@
       <c r="F322" s="10">
         <v>11864</v>
       </c>
-      <c r="G322" s="10">
+      <c r="G322" s="18">
         <v>20</v>
       </c>
-      <c r="H322" s="10">
+      <c r="H322" s="25">
         <v>13.125</v>
       </c>
-      <c r="I322" s="18">
+      <c r="I322" s="25">
         <v>13.125</v>
       </c>
       <c r="J322" s="18" t="b">
@@ -13908,13 +13924,13 @@
       <c r="F323" s="10">
         <v>11882</v>
       </c>
-      <c r="G323" s="10">
+      <c r="G323" s="18">
         <v>18</v>
       </c>
-      <c r="H323" s="10">
+      <c r="H323" s="25">
         <v>13.861111111111111</v>
       </c>
-      <c r="I323" s="18">
+      <c r="I323" s="25">
         <v>13.861111111111111</v>
       </c>
       <c r="J323" s="18" t="b">
@@ -13950,13 +13966,13 @@
       <c r="F324" s="10">
         <v>11907</v>
       </c>
-      <c r="G324" s="10">
+      <c r="G324" s="18">
         <v>25</v>
       </c>
-      <c r="H324" s="10">
+      <c r="H324" s="25">
         <v>13.1</v>
       </c>
-      <c r="I324" s="18">
+      <c r="I324" s="25">
         <v>13.1</v>
       </c>
       <c r="J324" s="18" t="b">
@@ -13992,13 +14008,13 @@
       <c r="F325" s="10">
         <v>11922</v>
       </c>
-      <c r="G325" s="10">
+      <c r="G325" s="18">
         <v>15</v>
       </c>
-      <c r="H325" s="10">
+      <c r="H325" s="25">
         <v>13.16666666666667</v>
       </c>
-      <c r="I325" s="18">
+      <c r="I325" s="25">
         <v>13.16666666666667</v>
       </c>
       <c r="J325" s="18" t="b">
@@ -14034,13 +14050,13 @@
       <c r="F326" s="10">
         <v>11940</v>
       </c>
-      <c r="G326" s="10">
+      <c r="G326" s="18">
         <v>18</v>
       </c>
-      <c r="H326" s="10">
+      <c r="H326" s="25">
         <v>13.388888888888889</v>
       </c>
-      <c r="I326" s="18">
+      <c r="I326" s="25">
         <v>13.388888888888889</v>
       </c>
       <c r="J326" s="18" t="b">
@@ -14076,9 +14092,9 @@
       <c r="F327" s="10">
         <v>11693</v>
       </c>
-      <c r="G327" s="10"/>
-      <c r="H327" s="10"/>
-      <c r="I327" s="18">
+      <c r="G327" s="18"/>
+      <c r="H327" s="25"/>
+      <c r="I327" s="25">
         <v>0</v>
       </c>
       <c r="J327" s="18" t="b">
@@ -14114,13 +14130,13 @@
       <c r="F328" s="10">
         <v>11982</v>
       </c>
-      <c r="G328" s="10">
+      <c r="G328" s="18">
         <v>289</v>
       </c>
-      <c r="H328" s="10">
+      <c r="H328" s="25">
         <v>0.87889273356401387</v>
       </c>
-      <c r="I328" s="18">
+      <c r="I328" s="25">
         <v>0</v>
       </c>
       <c r="J328" s="18" t="b">
@@ -14158,13 +14174,13 @@
       <c r="F329" s="10">
         <v>12002</v>
       </c>
-      <c r="G329" s="10">
+      <c r="G329" s="18">
         <v>20</v>
       </c>
-      <c r="H329" s="10">
+      <c r="H329" s="25">
         <v>13.25</v>
       </c>
-      <c r="I329" s="18">
+      <c r="I329" s="25">
         <v>13.25</v>
       </c>
       <c r="J329" s="18" t="b">
@@ -14200,13 +14216,13 @@
       <c r="F330" s="10">
         <v>12098</v>
       </c>
-      <c r="G330" s="10">
+      <c r="G330" s="18">
         <v>96</v>
       </c>
-      <c r="H330" s="10">
+      <c r="H330" s="25">
         <v>2.572916666666667</v>
       </c>
-      <c r="I330" s="18">
+      <c r="I330" s="25">
         <v>0</v>
       </c>
       <c r="J330" s="18" t="b">
@@ -14244,13 +14260,13 @@
       <c r="F331" s="10">
         <v>12115</v>
       </c>
-      <c r="G331" s="10">
+      <c r="G331" s="18">
         <v>17</v>
       </c>
-      <c r="H331" s="10">
+      <c r="H331" s="25">
         <v>14.441176470588241</v>
       </c>
-      <c r="I331" s="18">
+      <c r="I331" s="25">
         <v>14.441176470588241</v>
       </c>
       <c r="J331" s="18" t="b">
@@ -14286,13 +14302,13 @@
       <c r="F332" s="10">
         <v>12117.6</v>
       </c>
-      <c r="G332" s="10">
+      <c r="G332" s="18">
         <v>3</v>
       </c>
-      <c r="H332" s="10">
+      <c r="H332" s="25">
         <v>19.615384615381871</v>
       </c>
-      <c r="I332" s="18">
+      <c r="I332" s="25">
         <v>19.615384615381871</v>
       </c>
       <c r="J332" s="18" t="b">
@@ -14328,13 +14344,13 @@
       <c r="F333" s="10">
         <v>4727</v>
       </c>
-      <c r="G333" s="10">
+      <c r="G333" s="18">
         <v>26</v>
       </c>
-      <c r="H333" s="10">
+      <c r="H333" s="25">
         <v>11.769</v>
       </c>
-      <c r="I333" s="18">
+      <c r="I333" s="25">
         <v>11.769</v>
       </c>
       <c r="J333" s="18" t="b">
@@ -14370,13 +14386,13 @@
       <c r="F334" s="10">
         <v>4753.3</v>
       </c>
-      <c r="G334" s="10">
+      <c r="G334" s="18">
         <v>26</v>
       </c>
-      <c r="H334" s="10">
+      <c r="H334" s="25">
         <v>11.52091254752844</v>
       </c>
-      <c r="I334" s="18">
+      <c r="I334" s="25">
         <v>11.52091254752844</v>
       </c>
       <c r="J334" s="18" t="b">
@@ -14412,13 +14428,13 @@
       <c r="F335" s="10">
         <v>4777</v>
       </c>
-      <c r="G335" s="10">
+      <c r="G335" s="18">
         <v>24</v>
       </c>
-      <c r="H335" s="10">
+      <c r="H335" s="25">
         <v>11.85654008438828</v>
       </c>
-      <c r="I335" s="18">
+      <c r="I335" s="25">
         <v>11.85654008438828</v>
       </c>
       <c r="J335" s="18" t="b">
@@ -14454,13 +14470,13 @@
       <c r="F336" s="10">
         <v>4801</v>
       </c>
-      <c r="G336" s="10">
+      <c r="G336" s="18">
         <v>24</v>
       </c>
-      <c r="H336" s="10">
+      <c r="H336" s="25">
         <v>12.16666666666667</v>
       </c>
-      <c r="I336" s="18">
+      <c r="I336" s="25">
         <v>12.16666666666667</v>
       </c>
       <c r="J336" s="18" t="b">
@@ -14496,13 +14512,13 @@
       <c r="F337" s="10">
         <v>4825</v>
       </c>
-      <c r="G337" s="10">
+      <c r="G337" s="18">
         <v>24</v>
       </c>
-      <c r="H337" s="10">
+      <c r="H337" s="25">
         <v>10.5</v>
       </c>
-      <c r="I337" s="18">
+      <c r="I337" s="25">
         <v>10.5</v>
       </c>
       <c r="J337" s="18" t="b">
@@ -14538,13 +14554,13 @@
       <c r="F338" s="10">
         <v>4849</v>
       </c>
-      <c r="G338" s="10">
+      <c r="G338" s="18">
         <v>24</v>
       </c>
-      <c r="H338" s="10">
+      <c r="H338" s="25">
         <v>12.10416666666667</v>
       </c>
-      <c r="I338" s="18">
+      <c r="I338" s="25">
         <v>12.10416666666667</v>
       </c>
       <c r="J338" s="18" t="b">
@@ -14580,13 +14596,13 @@
       <c r="F339" s="10">
         <v>4897</v>
       </c>
-      <c r="G339" s="10">
+      <c r="G339" s="18">
         <v>22</v>
       </c>
-      <c r="H339" s="10">
+      <c r="H339" s="25">
         <v>13.95454545454546</v>
       </c>
-      <c r="I339" s="18">
+      <c r="I339" s="25">
         <v>13.95454545454546</v>
       </c>
       <c r="J339" s="18" t="b">
@@ -14622,13 +14638,13 @@
       <c r="F340" s="10">
         <v>4917</v>
       </c>
-      <c r="G340" s="10">
+      <c r="G340" s="18">
         <v>20</v>
       </c>
-      <c r="H340" s="10">
+      <c r="H340" s="25">
         <v>14.574999999999999</v>
       </c>
-      <c r="I340" s="18">
+      <c r="I340" s="25">
         <v>14.574999999999999</v>
       </c>
       <c r="J340" s="18" t="b">
@@ -14664,13 +14680,13 @@
       <c r="F341" s="10">
         <v>4940</v>
       </c>
-      <c r="G341" s="10">
+      <c r="G341" s="18">
         <v>23</v>
       </c>
-      <c r="H341" s="10">
+      <c r="H341" s="25">
         <v>13.34782608695652</v>
       </c>
-      <c r="I341" s="18">
+      <c r="I341" s="25">
         <v>13.34782608695652</v>
       </c>
       <c r="J341" s="18" t="b">
@@ -14706,13 +14722,13 @@
       <c r="F342" s="10">
         <v>4963</v>
       </c>
-      <c r="G342" s="10">
+      <c r="G342" s="18">
         <v>23</v>
       </c>
-      <c r="H342" s="10">
+      <c r="H342" s="25">
         <v>12.304347826086961</v>
       </c>
-      <c r="I342" s="18">
+      <c r="I342" s="25">
         <v>12.304347826086961</v>
       </c>
       <c r="J342" s="18" t="b">
@@ -14748,13 +14764,13 @@
       <c r="F343" s="10">
         <v>4985</v>
       </c>
-      <c r="G343" s="10">
+      <c r="G343" s="18">
         <v>22</v>
       </c>
-      <c r="H343" s="10">
+      <c r="H343" s="25">
         <v>12.79545454545454</v>
       </c>
-      <c r="I343" s="18">
+      <c r="I343" s="25">
         <v>12.79545454545454</v>
       </c>
       <c r="J343" s="18" t="b">
@@ -14790,13 +14806,13 @@
       <c r="F344" s="10">
         <v>5009</v>
       </c>
-      <c r="G344" s="10">
+      <c r="G344" s="18">
         <v>24</v>
       </c>
-      <c r="H344" s="10">
+      <c r="H344" s="25">
         <v>12.14583333333333</v>
       </c>
-      <c r="I344" s="18">
+      <c r="I344" s="25">
         <v>12.14583333333333</v>
       </c>
       <c r="J344" s="18" t="b">
@@ -14832,13 +14848,13 @@
       <c r="F345" s="10">
         <v>5032</v>
       </c>
-      <c r="G345" s="10">
+      <c r="G345" s="18">
         <v>23</v>
       </c>
-      <c r="H345" s="10">
+      <c r="H345" s="25">
         <v>12.239130434782609</v>
       </c>
-      <c r="I345" s="18">
+      <c r="I345" s="25">
         <v>12.239130434782609</v>
       </c>
       <c r="J345" s="18" t="b">
@@ -14874,13 +14890,13 @@
       <c r="F346" s="10">
         <v>5104</v>
       </c>
-      <c r="G346" s="10">
+      <c r="G346" s="18">
         <v>72</v>
       </c>
-      <c r="H346" s="10">
+      <c r="H346" s="25">
         <v>0.49305555555555558</v>
       </c>
-      <c r="I346" s="18">
+      <c r="I346" s="25">
         <v>0</v>
       </c>
       <c r="J346" s="18" t="b">
@@ -14918,11 +14934,11 @@
       <c r="F347" s="10">
         <v>5104</v>
       </c>
-      <c r="G347" s="10">
-        <v>0</v>
-      </c>
-      <c r="H347" s="10"/>
-      <c r="I347" s="18">
+      <c r="G347" s="18">
+        <v>0</v>
+      </c>
+      <c r="H347" s="25"/>
+      <c r="I347" s="25">
         <v>0</v>
       </c>
       <c r="J347" s="18" t="b">
@@ -14958,13 +14974,13 @@
       <c r="F348" s="10">
         <v>5126</v>
       </c>
-      <c r="G348" s="10">
+      <c r="G348" s="18">
         <v>22</v>
       </c>
-      <c r="H348" s="10">
+      <c r="H348" s="25">
         <v>13.31818181818182</v>
       </c>
-      <c r="I348" s="18">
+      <c r="I348" s="25">
         <v>13.31818181818182</v>
       </c>
       <c r="J348" s="18" t="b">
@@ -15000,13 +15016,13 @@
       <c r="F349" s="10">
         <v>5148.7</v>
       </c>
-      <c r="G349" s="10">
+      <c r="G349" s="18">
         <v>23</v>
       </c>
-      <c r="H349" s="10">
+      <c r="H349" s="25">
         <v>13.678414096916409</v>
       </c>
-      <c r="I349" s="18">
+      <c r="I349" s="25">
         <v>13.678414096916409</v>
       </c>
       <c r="J349" s="18" t="b">
@@ -15042,13 +15058,13 @@
       <c r="F350" s="10">
         <v>5173</v>
       </c>
-      <c r="G350" s="10">
+      <c r="G350" s="18">
         <v>24</v>
       </c>
-      <c r="H350" s="10">
+      <c r="H350" s="25">
         <v>12.24279835390937</v>
       </c>
-      <c r="I350" s="18">
+      <c r="I350" s="25">
         <v>12.24279835390937</v>
       </c>
       <c r="J350" s="18" t="b">
@@ -15084,13 +15100,13 @@
       <c r="F351" s="10">
         <v>5194.6000000000004</v>
       </c>
-      <c r="G351" s="10">
+      <c r="G351" s="18">
         <v>22</v>
       </c>
-      <c r="H351" s="10">
+      <c r="H351" s="25">
         <v>13.402777777777549</v>
       </c>
-      <c r="I351" s="18">
+      <c r="I351" s="25">
         <v>13.402777777777549</v>
       </c>
       <c r="J351" s="18" t="b">
@@ -15124,13 +15140,13 @@
       <c r="F352" s="10">
         <v>4875</v>
       </c>
-      <c r="G352" s="10">
+      <c r="G352" s="18">
         <v>26</v>
       </c>
-      <c r="H352" s="10">
+      <c r="H352" s="25">
         <v>11.38461538461539</v>
       </c>
-      <c r="I352" s="18">
+      <c r="I352" s="25">
         <v>11.38461538461539</v>
       </c>
       <c r="J352" s="18" t="b">
@@ -15166,13 +15182,13 @@
       <c r="F353" s="10">
         <v>10690.1</v>
       </c>
-      <c r="G353" s="10">
+      <c r="G353" s="18">
         <v>37</v>
       </c>
-      <c r="H353" s="10">
+      <c r="H353" s="25">
         <v>6.5359999999999996</v>
       </c>
-      <c r="I353" s="18">
+      <c r="I353" s="25">
         <v>6.5359999999999996</v>
       </c>
       <c r="J353" s="18" t="b">
@@ -15208,13 +15224,13 @@
       <c r="F354" s="10">
         <v>10703</v>
       </c>
-      <c r="G354" s="10">
+      <c r="G354" s="18">
         <v>13</v>
       </c>
-      <c r="H354" s="10">
+      <c r="H354" s="25">
         <v>17.94573643410903</v>
       </c>
-      <c r="I354" s="18">
+      <c r="I354" s="25">
         <v>17.94573643410903</v>
       </c>
       <c r="J354" s="18" t="b">
@@ -15250,13 +15266,13 @@
       <c r="F355" s="10">
         <v>10767</v>
       </c>
-      <c r="G355" s="10">
+      <c r="G355" s="18">
         <v>64</v>
       </c>
-      <c r="H355" s="10">
+      <c r="H355" s="25">
         <v>4.171875</v>
       </c>
-      <c r="I355" s="18">
+      <c r="I355" s="25">
         <v>4.171875</v>
       </c>
       <c r="J355" s="18" t="b">
@@ -15292,13 +15308,13 @@
       <c r="F356" s="10">
         <v>10785</v>
       </c>
-      <c r="G356" s="10">
+      <c r="G356" s="18">
         <v>18</v>
       </c>
-      <c r="H356" s="10">
+      <c r="H356" s="25">
         <v>11.444444444444439</v>
       </c>
-      <c r="I356" s="18">
+      <c r="I356" s="25">
         <v>11.444444444444439</v>
       </c>
       <c r="J356" s="18" t="b">
@@ -15334,13 +15350,13 @@
       <c r="F357" s="10">
         <v>10796</v>
       </c>
-      <c r="G357" s="10">
-        <v>11</v>
-      </c>
-      <c r="H357" s="10">
+      <c r="G357" s="18">
+        <v>11</v>
+      </c>
+      <c r="H357" s="25">
         <v>9.5</v>
       </c>
-      <c r="I357" s="18">
+      <c r="I357" s="25">
         <v>9.5</v>
       </c>
       <c r="J357" s="18" t="b">
@@ -15376,13 +15392,13 @@
       <c r="F358" s="10">
         <v>10815</v>
       </c>
-      <c r="G358" s="10">
+      <c r="G358" s="18">
         <v>19</v>
       </c>
-      <c r="H358" s="10">
+      <c r="H358" s="25">
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="I358" s="18">
+      <c r="I358" s="25">
         <v>0</v>
       </c>
       <c r="J358" s="18" t="b">
@@ -15420,13 +15436,13 @@
       <c r="F359" s="10">
         <v>10903</v>
       </c>
-      <c r="G359" s="10">
+      <c r="G359" s="18">
         <v>88</v>
       </c>
-      <c r="H359" s="10">
+      <c r="H359" s="25">
         <v>3.454545454545455</v>
       </c>
-      <c r="I359" s="18">
+      <c r="I359" s="25">
         <v>3.454545454545455</v>
       </c>
       <c r="J359" s="18" t="b">
@@ -15462,13 +15478,13 @@
       <c r="F360" s="10">
         <v>10990</v>
       </c>
-      <c r="G360" s="10">
+      <c r="G360" s="18">
         <v>87</v>
       </c>
-      <c r="H360" s="10">
+      <c r="H360" s="25">
         <v>3.327586206896552</v>
       </c>
-      <c r="I360" s="18">
+      <c r="I360" s="25">
         <v>3.327586206896552</v>
       </c>
       <c r="J360" s="18" t="b">
@@ -15504,13 +15520,13 @@
       <c r="F361" s="10">
         <v>10993</v>
       </c>
-      <c r="G361" s="10">
+      <c r="G361" s="18">
         <v>3</v>
       </c>
-      <c r="H361" s="10">
+      <c r="H361" s="25">
         <v>72.5</v>
       </c>
-      <c r="I361" s="18">
+      <c r="I361" s="25">
         <v>0</v>
       </c>
       <c r="J361" s="18" t="b">
@@ -15548,13 +15564,13 @@
       <c r="F362" s="10">
         <v>11000</v>
       </c>
-      <c r="G362" s="10">
+      <c r="G362" s="18">
         <v>7</v>
       </c>
-      <c r="H362" s="10">
+      <c r="H362" s="25">
         <v>40.571428571428569</v>
       </c>
-      <c r="I362" s="18">
+      <c r="I362" s="25">
         <v>0</v>
       </c>
       <c r="J362" s="18" t="b">
@@ -15592,13 +15608,13 @@
       <c r="F363" s="10">
         <v>11012</v>
       </c>
-      <c r="G363" s="10">
+      <c r="G363" s="18">
         <v>12</v>
       </c>
-      <c r="H363" s="10">
+      <c r="H363" s="25">
         <v>25.125</v>
       </c>
-      <c r="I363" s="18">
+      <c r="I363" s="25">
         <v>25.125</v>
       </c>
       <c r="J363" s="18" t="b">
@@ -15634,9 +15650,9 @@
       <c r="F364" s="10">
         <v>18</v>
       </c>
-      <c r="G364" s="10"/>
-      <c r="H364" s="10"/>
-      <c r="I364" s="18">
+      <c r="G364" s="18"/>
+      <c r="H364" s="25"/>
+      <c r="I364" s="25">
         <v>0</v>
       </c>
       <c r="J364" s="18" t="b">
@@ -15670,13 +15686,13 @@
       <c r="F365" s="10">
         <v>33</v>
       </c>
-      <c r="G365" s="10">
+      <c r="G365" s="18">
         <v>15</v>
       </c>
-      <c r="H365" s="10">
+      <c r="H365" s="25">
         <v>16.899999999999999</v>
       </c>
-      <c r="I365" s="18">
+      <c r="I365" s="25">
         <v>16.899999999999999</v>
       </c>
       <c r="J365" s="18" t="b">
@@ -15710,13 +15726,13 @@
       <c r="F366" s="10">
         <v>49</v>
       </c>
-      <c r="G366" s="10">
+      <c r="G366" s="18">
         <v>16</v>
       </c>
-      <c r="H366" s="10">
+      <c r="H366" s="25">
         <v>16.875</v>
       </c>
-      <c r="I366" s="18">
+      <c r="I366" s="25">
         <v>16.875</v>
       </c>
       <c r="J366" s="18" t="b">
@@ -15750,13 +15766,13 @@
       <c r="F367" s="10">
         <v>65</v>
       </c>
-      <c r="G367" s="10">
+      <c r="G367" s="18">
         <v>16</v>
       </c>
-      <c r="H367" s="10">
+      <c r="H367" s="25">
         <v>15.625</v>
       </c>
-      <c r="I367" s="18">
+      <c r="I367" s="25">
         <v>15.625</v>
       </c>
       <c r="J367" s="18" t="b">
@@ -15790,13 +15806,13 @@
       <c r="F368" s="10">
         <v>82.8</v>
       </c>
-      <c r="G368" s="10">
+      <c r="G368" s="18">
         <v>18</v>
       </c>
-      <c r="H368" s="10">
+      <c r="H368" s="25">
         <v>14.438202247191009</v>
       </c>
-      <c r="I368" s="18">
+      <c r="I368" s="25">
         <v>14.438202247191009</v>
       </c>
       <c r="J368" s="18" t="b">
@@ -15830,13 +15846,13 @@
       <c r="F369" s="10">
         <v>97</v>
       </c>
-      <c r="G369" s="10">
+      <c r="G369" s="18">
         <v>14</v>
       </c>
-      <c r="H369" s="10">
+      <c r="H369" s="25">
         <v>18.52112676056338</v>
       </c>
-      <c r="I369" s="18">
+      <c r="I369" s="25">
         <v>18.52112676056338</v>
       </c>
       <c r="J369" s="18" t="b">
@@ -15870,13 +15886,13 @@
       <c r="F370" s="10">
         <v>114</v>
       </c>
-      <c r="G370" s="10">
+      <c r="G370" s="18">
         <v>17</v>
       </c>
-      <c r="H370" s="10">
+      <c r="H370" s="25">
         <v>15.32352941176471</v>
       </c>
-      <c r="I370" s="18">
+      <c r="I370" s="25">
         <v>15.32352941176471</v>
       </c>
       <c r="J370" s="18" t="b">
@@ -15910,13 +15926,13 @@
       <c r="F371" s="10">
         <v>140</v>
       </c>
-      <c r="G371" s="10">
+      <c r="G371" s="18">
         <v>26</v>
       </c>
-      <c r="H371" s="10">
+      <c r="H371" s="25">
         <v>9.4615384615384617</v>
       </c>
-      <c r="I371" s="18">
+      <c r="I371" s="25">
         <v>9.4615384615384617</v>
       </c>
       <c r="J371" s="18" t="b">
@@ -15950,13 +15966,13 @@
       <c r="F372" s="10">
         <v>142</v>
       </c>
-      <c r="G372" s="10">
+      <c r="G372" s="18">
         <v>2</v>
       </c>
-      <c r="H372" s="10">
+      <c r="H372" s="25">
         <v>121</v>
       </c>
-      <c r="I372" s="18">
+      <c r="I372" s="25">
         <v>0</v>
       </c>
       <c r="J372" s="18" t="b">
@@ -15992,13 +16008,13 @@
       <c r="F373" s="10">
         <v>159</v>
       </c>
-      <c r="G373" s="10">
+      <c r="G373" s="18">
         <v>17</v>
       </c>
-      <c r="H373" s="10">
+      <c r="H373" s="25">
         <v>15.941176470588241</v>
       </c>
-      <c r="I373" s="18">
+      <c r="I373" s="25">
         <v>15.941176470588241</v>
       </c>
       <c r="J373" s="18" t="b">
@@ -16032,13 +16048,13 @@
       <c r="F374" s="10">
         <v>173</v>
       </c>
-      <c r="G374" s="10">
+      <c r="G374" s="18">
         <v>14</v>
       </c>
-      <c r="H374" s="10">
+      <c r="H374" s="25">
         <v>17.571428571428569</v>
       </c>
-      <c r="I374" s="18">
+      <c r="I374" s="25">
         <v>17.571428571428569</v>
       </c>
       <c r="J374" s="18" t="b">
@@ -16072,13 +16088,13 @@
       <c r="F375" s="14">
         <v>192</v>
       </c>
-      <c r="G375" s="14">
+      <c r="G375" s="22">
         <v>19</v>
       </c>
-      <c r="H375" s="14">
+      <c r="H375" s="26">
         <v>13.89473684210526</v>
       </c>
-      <c r="I375" s="22">
+      <c r="I375" s="26">
         <v>13.89473684210526</v>
       </c>
       <c r="J375" s="22" t="b">
